--- a/research/traditional_assets/database/data/lithuania/lithuania_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_business_consumer_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0978608650872024</v>
+        <v>0.09775232378957159</v>
       </c>
       <c r="C2">
-        <v>8.599789107201136</v>
+        <v>8.531461921185288</v>
       </c>
       <c r="D2">
-        <v>8.439789107201136</v>
+        <v>8.457421921185288</v>
       </c>
       <c r="E2">
-        <v>-0.076</v>
+        <v>0.009960000000000011</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.08596000000000001</v>
       </c>
       <c r="G2">
         <v>0.16</v>
@@ -1451,28 +1451,28 @@
         <v>0.715</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.004323788</v>
       </c>
       <c r="N2">
-        <v>0.715</v>
+        <v>0.710676212</v>
       </c>
       <c r="O2">
-        <v>0.10725</v>
+        <v>0.1066014318</v>
       </c>
       <c r="P2">
-        <v>0.60775</v>
+        <v>0.6040747801999999</v>
       </c>
       <c r="Q2">
-        <v>0.86675</v>
+        <v>0.8630747801999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0978608650872024</v>
+        <v>0.09830785231269858</v>
       </c>
       <c r="T2">
-        <v>0.9535130270927493</v>
+        <v>0.9616997551031415</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>165.3642593022599</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09775232378957159</v>
+        <v>0.09764378249194079</v>
       </c>
       <c r="C3">
-        <v>8.531461921185288</v>
+        <v>8.463208568073549</v>
       </c>
       <c r="D3">
-        <v>8.457421921185288</v>
+        <v>8.475128568073549</v>
       </c>
       <c r="E3">
-        <v>0.009960000000000011</v>
+        <v>0.09592000000000002</v>
       </c>
       <c r="F3">
-        <v>0.08596000000000001</v>
+        <v>0.17192</v>
       </c>
       <c r="G3">
         <v>0.16</v>
@@ -1533,28 +1533,28 @@
         <v>0.715</v>
       </c>
       <c r="M3">
-        <v>0.004323788</v>
+        <v>0.008647576000000001</v>
       </c>
       <c r="N3">
-        <v>0.710676212</v>
+        <v>0.706352424</v>
       </c>
       <c r="O3">
-        <v>0.1066014318</v>
+        <v>0.1059528636</v>
       </c>
       <c r="P3">
-        <v>0.6040747801999999</v>
+        <v>0.6003995604</v>
       </c>
       <c r="Q3">
-        <v>0.8630747801999999</v>
+        <v>0.8593995604</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09830785231269858</v>
+        <v>0.0987639617264702</v>
       </c>
       <c r="T3">
-        <v>0.9616997551031415</v>
+        <v>0.9700535591953787</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>165.3642593022599</v>
+        <v>82.68212965112997</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09764378249194079</v>
+        <v>0.09753524119430998</v>
       </c>
       <c r="C4">
-        <v>8.463208568073549</v>
+        <v>8.395029512573483</v>
       </c>
       <c r="D4">
-        <v>8.475128568073549</v>
+        <v>8.492909512573483</v>
       </c>
       <c r="E4">
-        <v>0.09592000000000002</v>
+        <v>0.18188</v>
       </c>
       <c r="F4">
-        <v>0.17192</v>
+        <v>0.25788</v>
       </c>
       <c r="G4">
         <v>0.16</v>
@@ -1615,28 +1615,28 @@
         <v>0.715</v>
       </c>
       <c r="M4">
-        <v>0.008647576000000001</v>
+        <v>0.012971364</v>
       </c>
       <c r="N4">
-        <v>0.706352424</v>
+        <v>0.702028636</v>
       </c>
       <c r="O4">
-        <v>0.1059528636</v>
+        <v>0.1053042954</v>
       </c>
       <c r="P4">
-        <v>0.6003995604</v>
+        <v>0.5967243406</v>
       </c>
       <c r="Q4">
-        <v>0.8593995604</v>
+        <v>0.8557243406</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0987639617264702</v>
+        <v>0.09922947545805152</v>
       </c>
       <c r="T4">
-        <v>0.9700535591953787</v>
+        <v>0.9785796066709607</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>82.68212965112997</v>
+        <v>55.12141976741999</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09753524119430998</v>
+        <v>0.09742669989667917</v>
       </c>
       <c r="C5">
-        <v>8.395029512573483</v>
+        <v>8.326925223300696</v>
       </c>
       <c r="D5">
-        <v>8.492909512573483</v>
+        <v>8.510765223300696</v>
       </c>
       <c r="E5">
-        <v>0.18188</v>
+        <v>0.26784</v>
       </c>
       <c r="F5">
-        <v>0.25788</v>
+        <v>0.34384</v>
       </c>
       <c r="G5">
         <v>0.16</v>
@@ -1697,28 +1697,28 @@
         <v>0.715</v>
       </c>
       <c r="M5">
-        <v>0.012971364</v>
+        <v>0.017295152</v>
       </c>
       <c r="N5">
-        <v>0.702028636</v>
+        <v>0.697704848</v>
       </c>
       <c r="O5">
-        <v>0.1053042954</v>
+        <v>0.1046557272</v>
       </c>
       <c r="P5">
-        <v>0.5967243406</v>
+        <v>0.5930491207999999</v>
       </c>
       <c r="Q5">
-        <v>0.8557243406</v>
+        <v>0.8520491207999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09922947545805152</v>
+        <v>0.09970468739237415</v>
       </c>
       <c r="T5">
-        <v>0.9785796066709607</v>
+        <v>0.9872832801356175</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>55.12141976741999</v>
+        <v>41.34106482556498</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09742669989667917</v>
+        <v>0.09731815859904837</v>
       </c>
       <c r="C6">
-        <v>8.326925223300696</v>
+        <v>8.258896172820021</v>
       </c>
       <c r="D6">
-        <v>8.510765223300696</v>
+        <v>8.528696172820021</v>
       </c>
       <c r="E6">
-        <v>0.26784</v>
+        <v>0.3538</v>
       </c>
       <c r="F6">
-        <v>0.34384</v>
+        <v>0.4298</v>
       </c>
       <c r="G6">
         <v>0.16</v>
@@ -1779,28 +1779,28 @@
         <v>0.715</v>
       </c>
       <c r="M6">
-        <v>0.017295152</v>
+        <v>0.02161894</v>
       </c>
       <c r="N6">
-        <v>0.697704848</v>
+        <v>0.69338106</v>
       </c>
       <c r="O6">
-        <v>0.1046557272</v>
+        <v>0.104007159</v>
       </c>
       <c r="P6">
-        <v>0.5930491207999999</v>
+        <v>0.589373901</v>
       </c>
       <c r="Q6">
-        <v>0.8520491207999999</v>
+        <v>0.848373901</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09970468739237415</v>
+        <v>0.100189903788472</v>
       </c>
       <c r="T6">
-        <v>0.9872832801356175</v>
+        <v>0.9961701888311092</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>41.34106482556498</v>
+        <v>33.07285186045199</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09731815859904837</v>
+        <v>0.09720961730141757</v>
       </c>
       <c r="C7">
-        <v>8.258896172820021</v>
+        <v>8.190942837687203</v>
       </c>
       <c r="D7">
-        <v>8.528696172820021</v>
+        <v>8.546702837687203</v>
       </c>
       <c r="E7">
-        <v>0.3538</v>
+        <v>0.43976</v>
       </c>
       <c r="F7">
-        <v>0.4298</v>
+        <v>0.51576</v>
       </c>
       <c r="G7">
         <v>0.16</v>
@@ -1861,28 +1861,28 @@
         <v>0.715</v>
       </c>
       <c r="M7">
-        <v>0.02161894</v>
+        <v>0.025942728</v>
       </c>
       <c r="N7">
-        <v>0.69338106</v>
+        <v>0.689057272</v>
       </c>
       <c r="O7">
-        <v>0.104007159</v>
+        <v>0.1033585908</v>
       </c>
       <c r="P7">
-        <v>0.589373901</v>
+        <v>0.5856986812</v>
       </c>
       <c r="Q7">
-        <v>0.848373901</v>
+        <v>0.8446986812</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.100189903788472</v>
+        <v>0.1006854439376783</v>
       </c>
       <c r="T7">
-        <v>0.9961701888311092</v>
+        <v>1.005246180690335</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>33.07285186045199</v>
+        <v>27.56070988371</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09720961730141756</v>
+        <v>0.09710107600378678</v>
       </c>
       <c r="C8">
-        <v>8.190942837687206</v>
+        <v>8.123065698491112</v>
       </c>
       <c r="D8">
-        <v>8.546702837687207</v>
+        <v>8.564785698491113</v>
       </c>
       <c r="E8">
-        <v>0.43976</v>
+        <v>0.52572</v>
       </c>
       <c r="F8">
-        <v>0.51576</v>
+        <v>0.6017199999999999</v>
       </c>
       <c r="G8">
         <v>0.16</v>
@@ -1943,28 +1943,28 @@
         <v>0.715</v>
       </c>
       <c r="M8">
-        <v>0.025942728</v>
+        <v>0.03026651599999999</v>
       </c>
       <c r="N8">
-        <v>0.689057272</v>
+        <v>0.684733484</v>
       </c>
       <c r="O8">
-        <v>0.1033585908</v>
+        <v>0.1027100226</v>
       </c>
       <c r="P8">
-        <v>0.5856986812</v>
+        <v>0.5820234614000001</v>
       </c>
       <c r="Q8">
-        <v>0.8446986812</v>
+        <v>0.8410234614000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1006854439376783</v>
+        <v>0.1011916408642868</v>
       </c>
       <c r="T8">
-        <v>1.005246180690335</v>
+        <v>1.014517355170189</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>27.56070988371</v>
+        <v>23.62346561460857</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09710107600378677</v>
+        <v>0.09699253470615599</v>
       </c>
       <c r="C9">
-        <v>8.123065698491114</v>
+        <v>8.055265239896515</v>
       </c>
       <c r="D9">
-        <v>8.564785698491114</v>
+        <v>8.582945239896516</v>
       </c>
       <c r="E9">
-        <v>0.5257200000000001</v>
+        <v>0.6116800000000001</v>
       </c>
       <c r="F9">
-        <v>0.60172</v>
+        <v>0.6876800000000001</v>
       </c>
       <c r="G9">
         <v>0.16</v>
@@ -2025,28 +2025,28 @@
         <v>0.715</v>
       </c>
       <c r="M9">
-        <v>0.030266516</v>
+        <v>0.034590304</v>
       </c>
       <c r="N9">
-        <v>0.684733484</v>
+        <v>0.680409696</v>
       </c>
       <c r="O9">
-        <v>0.1027100226</v>
+        <v>0.1020614544</v>
       </c>
       <c r="P9">
-        <v>0.5820234614000001</v>
+        <v>0.5783482416</v>
       </c>
       <c r="Q9">
-        <v>0.8410234614000001</v>
+        <v>0.8373482416</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1011916408642868</v>
+        <v>0.1017088420719087</v>
       </c>
       <c r="T9">
-        <v>1.014517355170189</v>
+        <v>1.023990076921344</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.62346561460857</v>
+        <v>20.6705324127825</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09699253470615599</v>
+        <v>0.09688399340852516</v>
       </c>
       <c r="C10">
-        <v>8.055265239896515</v>
+        <v>7.98754195068736</v>
       </c>
       <c r="D10">
-        <v>8.582945239896516</v>
+        <v>8.60118195068736</v>
       </c>
       <c r="E10">
-        <v>0.6116800000000001</v>
+        <v>0.69764</v>
       </c>
       <c r="F10">
-        <v>0.6876800000000001</v>
+        <v>0.77364</v>
       </c>
       <c r="G10">
         <v>0.16</v>
@@ -2107,28 +2107,28 @@
         <v>0.715</v>
       </c>
       <c r="M10">
-        <v>0.034590304</v>
+        <v>0.038914092</v>
       </c>
       <c r="N10">
-        <v>0.680409696</v>
+        <v>0.676085908</v>
       </c>
       <c r="O10">
-        <v>0.1020614544</v>
+        <v>0.1014128862</v>
       </c>
       <c r="P10">
-        <v>0.5783482416</v>
+        <v>0.5746730218</v>
       </c>
       <c r="Q10">
-        <v>0.8373482416</v>
+        <v>0.8336730218</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1017088420719087</v>
+        <v>0.1022374103390386</v>
       </c>
       <c r="T10">
-        <v>1.023990076921344</v>
+        <v>1.033670990359338</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.6705324127825</v>
+        <v>18.37380658914</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09688399340852516</v>
+        <v>0.09677545211089437</v>
       </c>
       <c r="C11">
-        <v>7.98754195068736</v>
+        <v>7.919896323810626</v>
       </c>
       <c r="D11">
-        <v>8.60118195068736</v>
+        <v>8.619496323810626</v>
       </c>
       <c r="E11">
-        <v>0.69764</v>
+        <v>0.7836</v>
       </c>
       <c r="F11">
-        <v>0.77364</v>
+        <v>0.8595999999999999</v>
       </c>
       <c r="G11">
         <v>0.16</v>
@@ -2189,28 +2189,28 @@
         <v>0.715</v>
       </c>
       <c r="M11">
-        <v>0.038914092</v>
+        <v>0.04323787999999999</v>
       </c>
       <c r="N11">
-        <v>0.676085908</v>
+        <v>0.67176212</v>
       </c>
       <c r="O11">
-        <v>0.1014128862</v>
+        <v>0.100764318</v>
       </c>
       <c r="P11">
-        <v>0.5746730218</v>
+        <v>0.5709978020000001</v>
       </c>
       <c r="Q11">
-        <v>0.8336730218</v>
+        <v>0.8299978020000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1022374103390386</v>
+        <v>0.1027777245676604</v>
       </c>
       <c r="T11">
-        <v>1.033670990359338</v>
+        <v>1.043567035207065</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.37380658914</v>
+        <v>16.536425930226</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09677545211089437</v>
+        <v>0.09666691081326358</v>
       </c>
       <c r="C12">
-        <v>7.919896323810626</v>
+        <v>7.852328856420771</v>
       </c>
       <c r="D12">
-        <v>8.619496323810626</v>
+        <v>8.637888856420771</v>
       </c>
       <c r="E12">
-        <v>0.7836000000000001</v>
+        <v>0.8695600000000001</v>
       </c>
       <c r="F12">
-        <v>0.8596</v>
+        <v>0.9455600000000001</v>
       </c>
       <c r="G12">
         <v>0.16</v>
@@ -2271,28 +2271,28 @@
         <v>0.715</v>
       </c>
       <c r="M12">
-        <v>0.04323788</v>
+        <v>0.047561668</v>
       </c>
       <c r="N12">
-        <v>0.67176212</v>
+        <v>0.6674383319999999</v>
       </c>
       <c r="O12">
-        <v>0.100764318</v>
+        <v>0.1001157498</v>
       </c>
       <c r="P12">
-        <v>0.5709978020000001</v>
+        <v>0.5673225821999999</v>
       </c>
       <c r="Q12">
-        <v>0.8299978020000001</v>
+        <v>0.8263225821999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1027777245676604</v>
+        <v>0.1033301806890602</v>
       </c>
       <c r="T12">
-        <v>1.043567035207065</v>
+        <v>1.053685463085078</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.536425930226</v>
+        <v>15.03311448202363</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09666691081326358</v>
+        <v>0.09655836951563275</v>
       </c>
       <c r="C13">
-        <v>7.852328856420771</v>
+        <v>7.784840049924691</v>
       </c>
       <c r="D13">
-        <v>8.637888856420771</v>
+        <v>8.656360049924691</v>
       </c>
       <c r="E13">
-        <v>0.8695600000000001</v>
+        <v>0.95552</v>
       </c>
       <c r="F13">
-        <v>0.9455600000000001</v>
+        <v>1.03152</v>
       </c>
       <c r="G13">
         <v>0.16</v>
@@ -2353,28 +2353,28 @@
         <v>0.715</v>
       </c>
       <c r="M13">
-        <v>0.047561668</v>
+        <v>0.051885456</v>
       </c>
       <c r="N13">
-        <v>0.6674383319999999</v>
+        <v>0.6631145439999999</v>
       </c>
       <c r="O13">
-        <v>0.1001157498</v>
+        <v>0.09946718159999998</v>
       </c>
       <c r="P13">
-        <v>0.5673225821999999</v>
+        <v>0.5636473623999999</v>
       </c>
       <c r="Q13">
-        <v>0.8263225821999999</v>
+        <v>0.8226473623999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1033301806890602</v>
+        <v>0.1038951926314009</v>
       </c>
       <c r="T13">
-        <v>1.053685463085078</v>
+        <v>1.064033855233045</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.03311448202363</v>
+        <v>13.780354941855</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09655836951563275</v>
+        <v>0.09661557821800194</v>
       </c>
       <c r="C14">
-        <v>7.784840049924691</v>
+        <v>7.689134630447771</v>
       </c>
       <c r="D14">
-        <v>8.656360049924691</v>
+        <v>8.646614630447772</v>
       </c>
       <c r="E14">
-        <v>0.95552</v>
+        <v>1.04148</v>
       </c>
       <c r="F14">
-        <v>1.03152</v>
+        <v>1.11748</v>
       </c>
       <c r="G14">
         <v>0.16</v>
@@ -2435,45 +2435,45 @@
         <v>0.715</v>
       </c>
       <c r="M14">
-        <v>0.051885456</v>
+        <v>0.057885464</v>
       </c>
       <c r="N14">
-        <v>0.6631145439999999</v>
+        <v>0.6571145359999999</v>
       </c>
       <c r="O14">
-        <v>0.09946718159999998</v>
+        <v>0.09856718039999998</v>
       </c>
       <c r="P14">
-        <v>0.5636473623999999</v>
+        <v>0.5585473555999999</v>
       </c>
       <c r="Q14">
-        <v>0.8226473623999999</v>
+        <v>0.8175473555999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1038951926314009</v>
+        <v>0.1044731933540252</v>
       </c>
       <c r="T14">
-        <v>1.064033855233045</v>
+        <v>1.07462014145338</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.15</v>
       </c>
       <c r="W14">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.780354941855</v>
+        <v>12.35197838269034</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09661557821800194</v>
+        <v>0.09651978692037114</v>
       </c>
       <c r="C15">
-        <v>7.689134630447771</v>
+        <v>7.619504952120149</v>
       </c>
       <c r="D15">
-        <v>8.646614630447772</v>
+        <v>8.662944952120149</v>
       </c>
       <c r="E15">
-        <v>1.04148</v>
+        <v>1.12744</v>
       </c>
       <c r="F15">
-        <v>1.11748</v>
+        <v>1.20344</v>
       </c>
       <c r="G15">
         <v>0.16</v>
@@ -2517,28 +2517,28 @@
         <v>0.715</v>
       </c>
       <c r="M15">
-        <v>0.057885464</v>
+        <v>0.062338192</v>
       </c>
       <c r="N15">
-        <v>0.6571145359999999</v>
+        <v>0.652661808</v>
       </c>
       <c r="O15">
-        <v>0.09856718039999998</v>
+        <v>0.09789927119999998</v>
       </c>
       <c r="P15">
-        <v>0.5585473555999999</v>
+        <v>0.5547625368</v>
       </c>
       <c r="Q15">
-        <v>0.8175473555999999</v>
+        <v>0.8137625368</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1044731933540252</v>
+        <v>0.1050646359539199</v>
       </c>
       <c r="T15">
-        <v>1.07462014145338</v>
+        <v>1.085452620376513</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.35197838269034</v>
+        <v>11.46969421249817</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09651978692037114</v>
+        <v>0.09642399562274033</v>
       </c>
       <c r="C16">
-        <v>7.619504952120149</v>
+        <v>7.549937074631615</v>
       </c>
       <c r="D16">
-        <v>8.662944952120149</v>
+        <v>8.679337074631615</v>
       </c>
       <c r="E16">
-        <v>1.12744</v>
+        <v>1.2134</v>
       </c>
       <c r="F16">
-        <v>1.20344</v>
+        <v>1.2894</v>
       </c>
       <c r="G16">
         <v>0.16</v>
@@ -2599,28 +2599,28 @@
         <v>0.715</v>
       </c>
       <c r="M16">
-        <v>0.062338192</v>
+        <v>0.06679092</v>
       </c>
       <c r="N16">
-        <v>0.652661808</v>
+        <v>0.64820908</v>
       </c>
       <c r="O16">
-        <v>0.09789927119999998</v>
+        <v>0.097231362</v>
       </c>
       <c r="P16">
-        <v>0.5547625368</v>
+        <v>0.5509777179999999</v>
       </c>
       <c r="Q16">
-        <v>0.8137625368</v>
+        <v>0.809977718</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1050646359539199</v>
+        <v>0.1056699948502828</v>
       </c>
       <c r="T16">
-        <v>1.085452620376513</v>
+        <v>1.096539981156662</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.46969421249817</v>
+        <v>10.70504793166496</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09642399562274033</v>
+        <v>0.09632820432510955</v>
       </c>
       <c r="C17">
-        <v>7.549937074631615</v>
+        <v>7.48043134946799</v>
       </c>
       <c r="D17">
-        <v>8.679337074631615</v>
+        <v>8.69579134946799</v>
       </c>
       <c r="E17">
-        <v>1.2134</v>
+        <v>1.29936</v>
       </c>
       <c r="F17">
-        <v>1.2894</v>
+        <v>1.37536</v>
       </c>
       <c r="G17">
         <v>0.16</v>
@@ -2681,28 +2681,28 @@
         <v>0.715</v>
       </c>
       <c r="M17">
-        <v>0.06679091999999999</v>
+        <v>0.07124364800000001</v>
       </c>
       <c r="N17">
-        <v>0.64820908</v>
+        <v>0.6437563519999999</v>
       </c>
       <c r="O17">
-        <v>0.097231362</v>
+        <v>0.09656345279999999</v>
       </c>
       <c r="P17">
-        <v>0.5509777179999999</v>
+        <v>0.5471928991999999</v>
       </c>
       <c r="Q17">
-        <v>0.809977718</v>
+        <v>0.8061928991999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1056699948502828</v>
+        <v>0.1062897670537018</v>
       </c>
       <c r="T17">
-        <v>1.096539981156662</v>
+        <v>1.10789132671729</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.70504793166496</v>
+        <v>10.0359824359359</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09632820432510955</v>
+        <v>0.09647806302747873</v>
       </c>
       <c r="C18">
-        <v>7.48043134946799</v>
+        <v>7.368757264717003</v>
       </c>
       <c r="D18">
-        <v>8.69579134946799</v>
+        <v>8.670077264717003</v>
       </c>
       <c r="E18">
-        <v>1.29936</v>
+        <v>1.38532</v>
       </c>
       <c r="F18">
-        <v>1.37536</v>
+        <v>1.46132</v>
       </c>
       <c r="G18">
         <v>0.16</v>
@@ -2763,45 +2763,45 @@
         <v>0.715</v>
       </c>
       <c r="M18">
-        <v>0.07124364800000001</v>
+        <v>0.07818062000000001</v>
       </c>
       <c r="N18">
-        <v>0.6437563519999999</v>
+        <v>0.6368193799999999</v>
       </c>
       <c r="O18">
-        <v>0.09656345279999999</v>
+        <v>0.09552290699999999</v>
       </c>
       <c r="P18">
-        <v>0.5471928991999999</v>
+        <v>0.5412964729999999</v>
       </c>
       <c r="Q18">
-        <v>0.8061928991999999</v>
+        <v>0.800296473</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1062897670537018</v>
+        <v>0.1069244735270828</v>
       </c>
       <c r="T18">
-        <v>1.10789132671729</v>
+        <v>1.119516198676969</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.15</v>
       </c>
       <c r="W18">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>10.0359824359359</v>
+        <v>9.145488997145327</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09647806302747873</v>
+        <v>0.09639672172984792</v>
       </c>
       <c r="C19">
-        <v>7.368757264717003</v>
+        <v>7.296735624973563</v>
       </c>
       <c r="D19">
-        <v>8.670077264717003</v>
+        <v>8.684015624973563</v>
       </c>
       <c r="E19">
-        <v>1.38532</v>
+        <v>1.47128</v>
       </c>
       <c r="F19">
-        <v>1.46132</v>
+        <v>1.54728</v>
       </c>
       <c r="G19">
         <v>0.16</v>
@@ -2845,28 +2845,28 @@
         <v>0.715</v>
       </c>
       <c r="M19">
-        <v>0.07818062000000001</v>
+        <v>0.08277948000000002</v>
       </c>
       <c r="N19">
-        <v>0.6368193799999999</v>
+        <v>0.63222052</v>
       </c>
       <c r="O19">
-        <v>0.09552290699999999</v>
+        <v>0.09483307799999999</v>
       </c>
       <c r="P19">
-        <v>0.5412964729999999</v>
+        <v>0.537387442</v>
       </c>
       <c r="Q19">
-        <v>0.800296473</v>
+        <v>0.796387442</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1069244735270828</v>
+        <v>0.107574660646156</v>
       </c>
       <c r="T19">
-        <v>1.119516198676969</v>
+        <v>1.131424604099079</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.145488997145327</v>
+        <v>8.637406275081698</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09639672172984794</v>
+        <v>0.09631538043221713</v>
       </c>
       <c r="C20">
-        <v>7.29673562497356</v>
+        <v>7.224758873115763</v>
       </c>
       <c r="D20">
-        <v>8.68401562497356</v>
+        <v>8.697998873115763</v>
       </c>
       <c r="E20">
-        <v>1.47128</v>
+        <v>1.55724</v>
       </c>
       <c r="F20">
-        <v>1.54728</v>
+        <v>1.63324</v>
       </c>
       <c r="G20">
         <v>0.16</v>
@@ -2927,28 +2927,28 @@
         <v>0.715</v>
       </c>
       <c r="M20">
-        <v>0.08277948</v>
+        <v>0.08737834</v>
       </c>
       <c r="N20">
-        <v>0.63222052</v>
+        <v>0.62762166</v>
       </c>
       <c r="O20">
-        <v>0.09483307799999999</v>
+        <v>0.094143249</v>
       </c>
       <c r="P20">
-        <v>0.537387442</v>
+        <v>0.5334784109999999</v>
       </c>
       <c r="Q20">
-        <v>0.796387442</v>
+        <v>0.7924784109999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.107574660646156</v>
+        <v>0.1082409017681693</v>
       </c>
       <c r="T20">
-        <v>1.131424604099079</v>
+        <v>1.14362704422297</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.637406275081698</v>
+        <v>8.182805944814241</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09631538043221713</v>
+        <v>0.09623403913458631</v>
       </c>
       <c r="C21">
-        <v>7.224758873115763</v>
+        <v>7.152827226332579</v>
       </c>
       <c r="D21">
-        <v>8.697998873115763</v>
+        <v>8.712027226332578</v>
       </c>
       <c r="E21">
-        <v>1.55724</v>
+        <v>1.6432</v>
       </c>
       <c r="F21">
-        <v>1.63324</v>
+        <v>1.7192</v>
       </c>
       <c r="G21">
         <v>0.16</v>
@@ -3009,28 +3009,28 @@
         <v>0.715</v>
       </c>
       <c r="M21">
-        <v>0.08737834</v>
+        <v>0.0919772</v>
       </c>
       <c r="N21">
-        <v>0.62762166</v>
+        <v>0.6230228</v>
       </c>
       <c r="O21">
-        <v>0.094143249</v>
+        <v>0.09345342</v>
       </c>
       <c r="P21">
-        <v>0.5334784109999999</v>
+        <v>0.52956938</v>
       </c>
       <c r="Q21">
-        <v>0.7924784109999999</v>
+        <v>0.78856938</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1082409017681693</v>
+        <v>0.1089237989182329</v>
       </c>
       <c r="T21">
-        <v>1.14362704422297</v>
+        <v>1.156134545349959</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.182805944814241</v>
+        <v>7.773665647573529</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09623403913458631</v>
+        <v>0.09629549783695554</v>
       </c>
       <c r="C22">
-        <v>7.152827226332579</v>
+        <v>7.056263708964265</v>
       </c>
       <c r="D22">
-        <v>8.712027226332578</v>
+        <v>8.701423708964265</v>
       </c>
       <c r="E22">
-        <v>1.6432</v>
+        <v>1.72916</v>
       </c>
       <c r="F22">
-        <v>1.7192</v>
+        <v>1.80516</v>
       </c>
       <c r="G22">
         <v>0.16</v>
@@ -3091,45 +3091,45 @@
         <v>0.715</v>
       </c>
       <c r="M22">
-        <v>0.0919772</v>
+        <v>0.09802018800000001</v>
       </c>
       <c r="N22">
-        <v>0.6230228</v>
+        <v>0.616979812</v>
       </c>
       <c r="O22">
-        <v>0.09345342</v>
+        <v>0.09254697179999999</v>
       </c>
       <c r="P22">
-        <v>0.52956938</v>
+        <v>0.5244328402</v>
       </c>
       <c r="Q22">
-        <v>0.78856938</v>
+        <v>0.7834328402</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1089237989182329</v>
+        <v>0.1096239846037412</v>
       </c>
       <c r="T22">
-        <v>1.156134545349959</v>
+        <v>1.168958692075099</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.15</v>
       </c>
       <c r="W22">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.773665647573529</v>
+        <v>7.294415717709089</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0962954978369555</v>
+        <v>0.09622095653932472</v>
       </c>
       <c r="C23">
-        <v>7.056263708964273</v>
+        <v>6.983167713517529</v>
       </c>
       <c r="D23">
-        <v>8.701423708964272</v>
+        <v>8.714287713517528</v>
       </c>
       <c r="E23">
-        <v>1.72916</v>
+        <v>1.81512</v>
       </c>
       <c r="F23">
-        <v>1.80516</v>
+        <v>1.89112</v>
       </c>
       <c r="G23">
         <v>0.16</v>
@@ -3173,28 +3173,28 @@
         <v>0.715</v>
       </c>
       <c r="M23">
-        <v>0.09802018799999999</v>
+        <v>0.102687816</v>
       </c>
       <c r="N23">
-        <v>0.616979812</v>
+        <v>0.612312184</v>
       </c>
       <c r="O23">
-        <v>0.09254697179999999</v>
+        <v>0.0918468276</v>
       </c>
       <c r="P23">
-        <v>0.5244328402</v>
+        <v>0.5204653564</v>
       </c>
       <c r="Q23">
-        <v>0.7834328402</v>
+        <v>0.7794653564</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1096239846037411</v>
+        <v>0.110342123768365</v>
       </c>
       <c r="T23">
-        <v>1.168958692075098</v>
+        <v>1.182111663075242</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.29441571770909</v>
+        <v>6.962851366904131</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09622095653932472</v>
+        <v>0.09614641524169393</v>
       </c>
       <c r="C24">
-        <v>6.983167713517529</v>
+        <v>6.910109810140999</v>
       </c>
       <c r="D24">
-        <v>8.714287713517528</v>
+        <v>8.727189810140999</v>
       </c>
       <c r="E24">
-        <v>1.81512</v>
+        <v>1.90108</v>
       </c>
       <c r="F24">
-        <v>1.89112</v>
+        <v>1.97708</v>
       </c>
       <c r="G24">
         <v>0.16</v>
@@ -3255,28 +3255,28 @@
         <v>0.715</v>
       </c>
       <c r="M24">
-        <v>0.102687816</v>
+        <v>0.107355444</v>
       </c>
       <c r="N24">
-        <v>0.612312184</v>
+        <v>0.607644556</v>
       </c>
       <c r="O24">
-        <v>0.0918468276</v>
+        <v>0.0911466834</v>
       </c>
       <c r="P24">
-        <v>0.5204653564</v>
+        <v>0.5164978726</v>
       </c>
       <c r="Q24">
-        <v>0.7794653564</v>
+        <v>0.7754978726</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.110342123768365</v>
+        <v>0.1110789158983038</v>
       </c>
       <c r="T24">
-        <v>1.182111663075242</v>
+        <v>1.195606269685779</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.962851366904131</v>
+        <v>6.660118698777865</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09614641524169393</v>
+        <v>0.09607187394406311</v>
       </c>
       <c r="C25">
-        <v>6.910109810140999</v>
+        <v>6.837090168279274</v>
       </c>
       <c r="D25">
-        <v>8.727189810140999</v>
+        <v>8.740130168279274</v>
       </c>
       <c r="E25">
-        <v>1.90108</v>
+        <v>1.98704</v>
       </c>
       <c r="F25">
-        <v>1.97708</v>
+        <v>2.06304</v>
       </c>
       <c r="G25">
         <v>0.16</v>
@@ -3337,28 +3337,28 @@
         <v>0.715</v>
       </c>
       <c r="M25">
-        <v>0.107355444</v>
+        <v>0.112023072</v>
       </c>
       <c r="N25">
-        <v>0.607644556</v>
+        <v>0.6029769279999999</v>
       </c>
       <c r="O25">
-        <v>0.0911466834</v>
+        <v>0.09044653919999998</v>
       </c>
       <c r="P25">
-        <v>0.5164978726</v>
+        <v>0.5125303887999999</v>
       </c>
       <c r="Q25">
-        <v>0.7754978726</v>
+        <v>0.7715303887999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1110789158983038</v>
+        <v>0.1118350972948199</v>
       </c>
       <c r="T25">
-        <v>1.195606269685779</v>
+        <v>1.209455997522908</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.660118698777865</v>
+        <v>6.382613752995454</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09607187394406311</v>
+        <v>0.0959973326464323</v>
       </c>
       <c r="C26">
-        <v>6.837090168279274</v>
+        <v>6.764108958383413</v>
       </c>
       <c r="D26">
-        <v>8.740130168279274</v>
+        <v>8.753108958383413</v>
       </c>
       <c r="E26">
-        <v>1.98704</v>
+        <v>2.073</v>
       </c>
       <c r="F26">
-        <v>2.06304</v>
+        <v>2.149</v>
       </c>
       <c r="G26">
         <v>0.16</v>
@@ -3419,28 +3419,28 @@
         <v>0.715</v>
       </c>
       <c r="M26">
-        <v>0.112023072</v>
+        <v>0.1166907</v>
       </c>
       <c r="N26">
-        <v>0.6029769279999999</v>
+        <v>0.5983092999999999</v>
       </c>
       <c r="O26">
-        <v>0.09044653919999998</v>
+        <v>0.08974639499999999</v>
       </c>
       <c r="P26">
-        <v>0.5125303887999999</v>
+        <v>0.5085629049999999</v>
       </c>
       <c r="Q26">
-        <v>0.7715303887999999</v>
+        <v>0.7675629049999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1118350972948199</v>
+        <v>0.1126114435285764</v>
       </c>
       <c r="T26">
-        <v>1.209455997522908</v>
+        <v>1.223675051435695</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.382613752995454</v>
+        <v>6.127309202875635</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0959973326464323</v>
+        <v>0.09614379134880151</v>
       </c>
       <c r="C27">
-        <v>6.764108958383413</v>
+        <v>6.652684666851232</v>
       </c>
       <c r="D27">
-        <v>8.753108958383413</v>
+        <v>8.727644666851232</v>
       </c>
       <c r="E27">
-        <v>2.073</v>
+        <v>2.15896</v>
       </c>
       <c r="F27">
-        <v>2.149</v>
+        <v>2.23496</v>
       </c>
       <c r="G27">
         <v>0.16</v>
@@ -3501,45 +3501,45 @@
         <v>0.715</v>
       </c>
       <c r="M27">
-        <v>0.1166907</v>
+        <v>0.123593288</v>
       </c>
       <c r="N27">
-        <v>0.5983092999999999</v>
+        <v>0.5914067119999999</v>
       </c>
       <c r="O27">
-        <v>0.08974639499999999</v>
+        <v>0.08871100679999999</v>
       </c>
       <c r="P27">
-        <v>0.5085629049999999</v>
+        <v>0.5026957052</v>
       </c>
       <c r="Q27">
-        <v>0.7675629049999999</v>
+        <v>0.7616957052</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1126114435285764</v>
+        <v>0.113408772092975</v>
       </c>
       <c r="T27">
-        <v>1.223675051435695</v>
+        <v>1.238278404102881</v>
       </c>
       <c r="U27">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.15</v>
       </c>
       <c r="W27">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.127309202875635</v>
+        <v>5.785103799487881</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09614379134880151</v>
+        <v>0.09607775005117071</v>
       </c>
       <c r="C28">
-        <v>6.652684666851232</v>
+        <v>6.578188683806501</v>
       </c>
       <c r="D28">
-        <v>8.727644666851232</v>
+        <v>8.739108683806501</v>
       </c>
       <c r="E28">
-        <v>2.15896</v>
+        <v>2.24492</v>
       </c>
       <c r="F28">
-        <v>2.23496</v>
+        <v>2.32092</v>
       </c>
       <c r="G28">
         <v>0.16</v>
@@ -3583,28 +3583,28 @@
         <v>0.715</v>
       </c>
       <c r="M28">
-        <v>0.123593288</v>
+        <v>0.128346876</v>
       </c>
       <c r="N28">
-        <v>0.5914067119999999</v>
+        <v>0.5866531239999999</v>
       </c>
       <c r="O28">
-        <v>0.08871100679999999</v>
+        <v>0.08799796859999999</v>
       </c>
       <c r="P28">
-        <v>0.5026957052</v>
+        <v>0.4986551553999999</v>
       </c>
       <c r="Q28">
-        <v>0.7616957052</v>
+        <v>0.7576551553999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.113408772092975</v>
+        <v>0.1142279452755763</v>
       </c>
       <c r="T28">
-        <v>1.238278404102881</v>
+        <v>1.253281848623963</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.785103799487881</v>
+        <v>5.570840695803144</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09607775005117071</v>
+        <v>0.0960117087535399</v>
       </c>
       <c r="C29">
-        <v>6.578188683806501</v>
+        <v>6.503722857017139</v>
       </c>
       <c r="D29">
-        <v>8.739108683806501</v>
+        <v>8.750602857017139</v>
       </c>
       <c r="E29">
-        <v>2.24492</v>
+        <v>2.33088</v>
       </c>
       <c r="F29">
-        <v>2.32092</v>
+        <v>2.40688</v>
       </c>
       <c r="G29">
         <v>0.16</v>
@@ -3665,28 +3665,28 @@
         <v>0.715</v>
       </c>
       <c r="M29">
-        <v>0.128346876</v>
+        <v>0.133100464</v>
       </c>
       <c r="N29">
-        <v>0.5866531239999999</v>
+        <v>0.581899536</v>
       </c>
       <c r="O29">
-        <v>0.08799796859999999</v>
+        <v>0.0872849304</v>
       </c>
       <c r="P29">
-        <v>0.4986551553999999</v>
+        <v>0.4946146056</v>
       </c>
       <c r="Q29">
-        <v>0.7576551553999999</v>
+        <v>0.7536146055999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1142279452755763</v>
+        <v>0.1150698732688054</v>
       </c>
       <c r="T29">
-        <v>1.253281848623963</v>
+        <v>1.268702055492853</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.570840695803144</v>
+        <v>5.371882099524461</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0960117087535399</v>
+        <v>0.09594566745590909</v>
       </c>
       <c r="C30">
-        <v>6.503722857017139</v>
+        <v>6.429287305629521</v>
       </c>
       <c r="D30">
-        <v>8.750602857017139</v>
+        <v>8.762127305629521</v>
       </c>
       <c r="E30">
-        <v>2.33088</v>
+        <v>2.41684</v>
       </c>
       <c r="F30">
-        <v>2.40688</v>
+        <v>2.49284</v>
       </c>
       <c r="G30">
         <v>0.16</v>
@@ -3747,28 +3747,28 @@
         <v>0.715</v>
       </c>
       <c r="M30">
-        <v>0.133100464</v>
+        <v>0.137854052</v>
       </c>
       <c r="N30">
-        <v>0.581899536</v>
+        <v>0.577145948</v>
       </c>
       <c r="O30">
-        <v>0.0872849304</v>
+        <v>0.08657189219999999</v>
       </c>
       <c r="P30">
-        <v>0.4946146056</v>
+        <v>0.4905740558</v>
       </c>
       <c r="Q30">
-        <v>0.7536146055999999</v>
+        <v>0.7495740557999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1150698732688054</v>
+        <v>0.1159355175435339</v>
       </c>
       <c r="T30">
-        <v>1.268702055492853</v>
+        <v>1.284556634386218</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.371882099524461</v>
+        <v>5.186644785747755</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09594566745590909</v>
+        <v>0.09587962615827829</v>
       </c>
       <c r="C31">
-        <v>6.429287305629522</v>
+        <v>6.354882149418515</v>
       </c>
       <c r="D31">
-        <v>8.762127305629521</v>
+        <v>8.773682149418514</v>
       </c>
       <c r="E31">
-        <v>2.41684</v>
+        <v>2.5028</v>
       </c>
       <c r="F31">
-        <v>2.49284</v>
+        <v>2.5788</v>
       </c>
       <c r="G31">
         <v>0.16</v>
@@ -3829,28 +3829,28 @@
         <v>0.715</v>
       </c>
       <c r="M31">
-        <v>0.137854052</v>
+        <v>0.14260764</v>
       </c>
       <c r="N31">
-        <v>0.577145948</v>
+        <v>0.57239236</v>
       </c>
       <c r="O31">
-        <v>0.08657189219999999</v>
+        <v>0.085858854</v>
       </c>
       <c r="P31">
-        <v>0.4905740558</v>
+        <v>0.4865335060000001</v>
       </c>
       <c r="Q31">
-        <v>0.7495740557999999</v>
+        <v>0.7455335060000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1159355175435339</v>
+        <v>0.1168258945118261</v>
       </c>
       <c r="T31">
-        <v>1.284556634386218</v>
+        <v>1.300864201247965</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.186644785747756</v>
+        <v>5.013756626222832</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09587962615827829</v>
+        <v>0.09581358486064749</v>
       </c>
       <c r="C32">
-        <v>6.354882149418515</v>
+        <v>6.280507508791617</v>
       </c>
       <c r="D32">
-        <v>8.773682149418514</v>
+        <v>8.785267508791616</v>
       </c>
       <c r="E32">
-        <v>2.5028</v>
+        <v>2.58876</v>
       </c>
       <c r="F32">
-        <v>2.5788</v>
+        <v>2.66476</v>
       </c>
       <c r="G32">
         <v>0.16</v>
@@ -3911,28 +3911,28 @@
         <v>0.715</v>
       </c>
       <c r="M32">
-        <v>0.14260764</v>
+        <v>0.147361228</v>
       </c>
       <c r="N32">
-        <v>0.57239236</v>
+        <v>0.567638772</v>
       </c>
       <c r="O32">
-        <v>0.085858854</v>
+        <v>0.0851458158</v>
       </c>
       <c r="P32">
-        <v>0.4865335060000001</v>
+        <v>0.4824929562</v>
       </c>
       <c r="Q32">
-        <v>0.7455335060000001</v>
+        <v>0.7414929562</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1168258945118261</v>
+        <v>0.1177420795081848</v>
       </c>
       <c r="T32">
-        <v>1.300864201247965</v>
+        <v>1.317644451207154</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.013756626222832</v>
+        <v>4.852022541505965</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09581358486064749</v>
+        <v>0.09574754356301668</v>
       </c>
       <c r="C33">
-        <v>6.280507508791617</v>
+        <v>6.206163504793149</v>
       </c>
       <c r="D33">
-        <v>8.785267508791616</v>
+        <v>8.796883504793149</v>
       </c>
       <c r="E33">
-        <v>2.58876</v>
+        <v>2.67472</v>
       </c>
       <c r="F33">
-        <v>2.66476</v>
+        <v>2.75072</v>
       </c>
       <c r="G33">
         <v>0.16</v>
@@ -3993,28 +3993,28 @@
         <v>0.715</v>
       </c>
       <c r="M33">
-        <v>0.147361228</v>
+        <v>0.152114816</v>
       </c>
       <c r="N33">
-        <v>0.567638772</v>
+        <v>0.562885184</v>
       </c>
       <c r="O33">
-        <v>0.0851458158</v>
+        <v>0.08443277759999999</v>
       </c>
       <c r="P33">
-        <v>0.4824929562</v>
+        <v>0.4784524064</v>
       </c>
       <c r="Q33">
-        <v>0.7414929562</v>
+        <v>0.7374524064</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1177420795081848</v>
+        <v>0.1186852111220834</v>
       </c>
       <c r="T33">
-        <v>1.317644451207154</v>
+        <v>1.334918237929849</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.852022541505965</v>
+        <v>4.700396837083904</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09574754356301668</v>
+        <v>0.09568150226538587</v>
       </c>
       <c r="C34">
-        <v>6.206163504793149</v>
+        <v>6.131850259108462</v>
       </c>
       <c r="D34">
-        <v>8.796883504793149</v>
+        <v>8.808530259108462</v>
       </c>
       <c r="E34">
-        <v>2.67472</v>
+        <v>2.76068</v>
       </c>
       <c r="F34">
-        <v>2.75072</v>
+        <v>2.83668</v>
       </c>
       <c r="G34">
         <v>0.16</v>
@@ -4075,28 +4075,28 @@
         <v>0.715</v>
       </c>
       <c r="M34">
-        <v>0.152114816</v>
+        <v>0.156868404</v>
       </c>
       <c r="N34">
-        <v>0.562885184</v>
+        <v>0.558131596</v>
       </c>
       <c r="O34">
-        <v>0.08443277759999999</v>
+        <v>0.08371973939999999</v>
       </c>
       <c r="P34">
-        <v>0.4784524064</v>
+        <v>0.4744118566</v>
       </c>
       <c r="Q34">
-        <v>0.7374524064</v>
+        <v>0.7334118566</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1186852111220834</v>
+        <v>0.1196564959184864</v>
       </c>
       <c r="T34">
-        <v>1.334918237929849</v>
+        <v>1.352707660077102</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.700396837083904</v>
+        <v>4.557960569293481</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09568150226538587</v>
+        <v>0.09633796096775507</v>
       </c>
       <c r="C35">
-        <v>6.131850259108462</v>
+        <v>5.931472577173023</v>
       </c>
       <c r="D35">
-        <v>8.808530259108462</v>
+        <v>8.694112577173023</v>
       </c>
       <c r="E35">
-        <v>2.76068</v>
+        <v>2.84664</v>
       </c>
       <c r="F35">
-        <v>2.83668</v>
+        <v>2.92264</v>
       </c>
       <c r="G35">
         <v>0.16</v>
@@ -4157,45 +4157,45 @@
         <v>0.715</v>
       </c>
       <c r="M35">
-        <v>0.156868404</v>
+        <v>0.168928592</v>
       </c>
       <c r="N35">
-        <v>0.558131596</v>
+        <v>0.546071408</v>
       </c>
       <c r="O35">
-        <v>0.08371973939999999</v>
+        <v>0.0819107112</v>
       </c>
       <c r="P35">
-        <v>0.4744118566</v>
+        <v>0.4641606968</v>
       </c>
       <c r="Q35">
-        <v>0.7334118566</v>
+        <v>0.7231606967999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1196564959184864</v>
+        <v>0.1206572135875077</v>
       </c>
       <c r="T35">
-        <v>1.352707660077102</v>
+        <v>1.371036155622756</v>
       </c>
       <c r="U35">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V35">
         <v>0.15</v>
       </c>
       <c r="W35">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.557960569293481</v>
+        <v>4.232557624111375</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09633796096775507</v>
+        <v>0.09629316967012427</v>
       </c>
       <c r="C36">
-        <v>5.931472577173023</v>
+        <v>5.853224918993193</v>
       </c>
       <c r="D36">
-        <v>8.694112577173023</v>
+        <v>8.701824918993193</v>
       </c>
       <c r="E36">
-        <v>2.84664</v>
+        <v>2.9326</v>
       </c>
       <c r="F36">
-        <v>2.92264</v>
+        <v>3.0086</v>
       </c>
       <c r="G36">
         <v>0.16</v>
@@ -4239,28 +4239,28 @@
         <v>0.715</v>
       </c>
       <c r="M36">
-        <v>0.168928592</v>
+        <v>0.17389708</v>
       </c>
       <c r="N36">
-        <v>0.546071408</v>
+        <v>0.5411029199999999</v>
       </c>
       <c r="O36">
-        <v>0.0819107112</v>
+        <v>0.08116543799999999</v>
       </c>
       <c r="P36">
-        <v>0.4641606968</v>
+        <v>0.459937482</v>
       </c>
       <c r="Q36">
-        <v>0.7231606967999999</v>
+        <v>0.718937482</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1206572135875077</v>
+        <v>0.121688722569422</v>
       </c>
       <c r="T36">
-        <v>1.371036155622756</v>
+        <v>1.389928604877508</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.232557624111375</v>
+        <v>4.111627406279622</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09629316967012427</v>
+        <v>0.09731937837249346</v>
       </c>
       <c r="C37">
-        <v>5.853224918993193</v>
+        <v>5.59393424730303</v>
       </c>
       <c r="D37">
-        <v>8.701824918993193</v>
+        <v>8.52849424730303</v>
       </c>
       <c r="E37">
-        <v>2.9326</v>
+        <v>3.01856</v>
       </c>
       <c r="F37">
-        <v>3.0086</v>
+        <v>3.09456</v>
       </c>
       <c r="G37">
         <v>0.16</v>
@@ -4321,45 +4321,45 @@
         <v>0.715</v>
       </c>
       <c r="M37">
-        <v>0.17389708</v>
+        <v>0.189696528</v>
       </c>
       <c r="N37">
-        <v>0.5411029199999999</v>
+        <v>0.5253034719999999</v>
       </c>
       <c r="O37">
-        <v>0.08116543799999999</v>
+        <v>0.07879552079999999</v>
       </c>
       <c r="P37">
-        <v>0.459937482</v>
+        <v>0.4465079512</v>
       </c>
       <c r="Q37">
-        <v>0.718937482</v>
+        <v>0.7055079512</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.121688722569422</v>
+        <v>0.122752466207021</v>
       </c>
       <c r="T37">
-        <v>1.389928604877508</v>
+        <v>1.40941144317147</v>
       </c>
       <c r="U37">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V37">
         <v>0.15</v>
       </c>
       <c r="W37">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.111627406279622</v>
+        <v>3.769178105357837</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09731937837249346</v>
+        <v>0.09730433707486266</v>
       </c>
       <c r="C38">
-        <v>5.59393424730303</v>
+        <v>5.510464903966174</v>
       </c>
       <c r="D38">
-        <v>8.52849424730303</v>
+        <v>8.530984903966173</v>
       </c>
       <c r="E38">
-        <v>3.01856</v>
+        <v>3.10452</v>
       </c>
       <c r="F38">
-        <v>3.09456</v>
+        <v>3.18052</v>
       </c>
       <c r="G38">
         <v>0.16</v>
@@ -4403,28 +4403,28 @@
         <v>0.715</v>
       </c>
       <c r="M38">
-        <v>0.189696528</v>
+        <v>0.194965876</v>
       </c>
       <c r="N38">
-        <v>0.5253034719999999</v>
+        <v>0.5200341239999999</v>
       </c>
       <c r="O38">
-        <v>0.07879552079999999</v>
+        <v>0.07800511859999999</v>
       </c>
       <c r="P38">
-        <v>0.4465079512</v>
+        <v>0.4420290054</v>
       </c>
       <c r="Q38">
-        <v>0.7055079512</v>
+        <v>0.7010290053999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.122752466207021</v>
+        <v>0.123849979483909</v>
       </c>
       <c r="T38">
-        <v>1.40941144317147</v>
+        <v>1.429512784268415</v>
       </c>
       <c r="U38">
         <v>0.0613</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.769178105357837</v>
+        <v>3.667308426834652</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09730433707486266</v>
+        <v>0.09728929577723186</v>
       </c>
       <c r="C39">
-        <v>5.510464903966174</v>
+        <v>5.426997015794226</v>
       </c>
       <c r="D39">
-        <v>8.530984903966173</v>
+        <v>8.533477015794226</v>
       </c>
       <c r="E39">
-        <v>3.10452</v>
+        <v>3.19048</v>
       </c>
       <c r="F39">
-        <v>3.18052</v>
+        <v>3.26648</v>
       </c>
       <c r="G39">
         <v>0.16</v>
@@ -4485,28 +4485,28 @@
         <v>0.715</v>
       </c>
       <c r="M39">
-        <v>0.194965876</v>
+        <v>0.200235224</v>
       </c>
       <c r="N39">
-        <v>0.5200341239999999</v>
+        <v>0.5147647759999999</v>
       </c>
       <c r="O39">
-        <v>0.07800511859999999</v>
+        <v>0.07721471639999998</v>
       </c>
       <c r="P39">
-        <v>0.4420290054</v>
+        <v>0.4375500595999999</v>
       </c>
       <c r="Q39">
-        <v>0.7010290053999999</v>
+        <v>0.6965500595999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.123849979483909</v>
+        <v>0.1249828964148901</v>
       </c>
       <c r="T39">
-        <v>1.429512784268415</v>
+        <v>1.450262555723327</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.667308426834652</v>
+        <v>3.570800310339004</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09728929577723186</v>
+        <v>0.09820245447960105</v>
       </c>
       <c r="C40">
-        <v>5.426997015794226</v>
+        <v>5.192333698825106</v>
       </c>
       <c r="D40">
-        <v>8.533477015794226</v>
+        <v>8.384773698825105</v>
       </c>
       <c r="E40">
-        <v>3.19048</v>
+        <v>3.27644</v>
       </c>
       <c r="F40">
-        <v>3.26648</v>
+        <v>3.35244</v>
       </c>
       <c r="G40">
         <v>0.16</v>
@@ -4567,45 +4567,45 @@
         <v>0.715</v>
       </c>
       <c r="M40">
-        <v>0.200235224</v>
+        <v>0.214891404</v>
       </c>
       <c r="N40">
-        <v>0.5147647759999999</v>
+        <v>0.500108596</v>
       </c>
       <c r="O40">
-        <v>0.07721471639999998</v>
+        <v>0.07501628940000001</v>
       </c>
       <c r="P40">
-        <v>0.4375500595999999</v>
+        <v>0.4250923066</v>
       </c>
       <c r="Q40">
-        <v>0.6965500595999999</v>
+        <v>0.6840923066</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1249828964148901</v>
+        <v>0.1261529581632804</v>
       </c>
       <c r="T40">
-        <v>1.450262555723327</v>
+        <v>1.471692647553809</v>
       </c>
       <c r="U40">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V40">
         <v>0.15</v>
       </c>
       <c r="W40">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.570800310339004</v>
+        <v>3.327261987640976</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09820245447960105</v>
+        <v>0.09821121318197024</v>
       </c>
       <c r="C41">
-        <v>5.192333698825106</v>
+        <v>5.10497247697195</v>
       </c>
       <c r="D41">
-        <v>8.384773698825105</v>
+        <v>8.38337247697195</v>
       </c>
       <c r="E41">
-        <v>3.27644</v>
+        <v>3.3624</v>
       </c>
       <c r="F41">
-        <v>3.35244</v>
+        <v>3.4384</v>
       </c>
       <c r="G41">
         <v>0.16</v>
@@ -4649,28 +4649,28 @@
         <v>0.715</v>
       </c>
       <c r="M41">
-        <v>0.214891404</v>
+        <v>0.22040144</v>
       </c>
       <c r="N41">
-        <v>0.500108596</v>
+        <v>0.4945985599999999</v>
       </c>
       <c r="O41">
-        <v>0.07501628940000001</v>
+        <v>0.07418978399999998</v>
       </c>
       <c r="P41">
-        <v>0.4250923066</v>
+        <v>0.4204087759999999</v>
       </c>
       <c r="Q41">
-        <v>0.6840923066</v>
+        <v>0.6794087759999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1261529581632804</v>
+        <v>0.1273620219699504</v>
       </c>
       <c r="T41">
-        <v>1.471692647553809</v>
+        <v>1.493837075778641</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.327261987640976</v>
+        <v>3.244080437949951</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09821121318197024</v>
+        <v>0.09821997188433945</v>
       </c>
       <c r="C42">
-        <v>5.10497247697195</v>
+        <v>5.017611723371049</v>
       </c>
       <c r="D42">
-        <v>8.38337247697195</v>
+        <v>8.381971723371048</v>
       </c>
       <c r="E42">
-        <v>3.3624</v>
+        <v>3.44836</v>
       </c>
       <c r="F42">
-        <v>3.4384</v>
+        <v>3.52436</v>
       </c>
       <c r="G42">
         <v>0.16</v>
@@ -4731,28 +4731,28 @@
         <v>0.715</v>
       </c>
       <c r="M42">
-        <v>0.22040144</v>
+        <v>0.225911476</v>
       </c>
       <c r="N42">
-        <v>0.4945985599999999</v>
+        <v>0.4890885239999999</v>
       </c>
       <c r="O42">
-        <v>0.07418978399999998</v>
+        <v>0.07336327859999998</v>
       </c>
       <c r="P42">
-        <v>0.4204087759999999</v>
+        <v>0.4157252453999999</v>
       </c>
       <c r="Q42">
-        <v>0.6794087759999999</v>
+        <v>0.6747252453999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1273620219699504</v>
+        <v>0.1286120709904058</v>
       </c>
       <c r="T42">
-        <v>1.493837075778641</v>
+        <v>1.516732162587365</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.244080437949951</v>
+        <v>3.164956524829221</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09821997188433945</v>
+        <v>0.09822873058670864</v>
       </c>
       <c r="C43">
-        <v>5.017611723371049</v>
+        <v>4.930251437787737</v>
       </c>
       <c r="D43">
-        <v>8.381971723371048</v>
+        <v>8.380571437787736</v>
       </c>
       <c r="E43">
-        <v>3.44836</v>
+        <v>3.53432</v>
       </c>
       <c r="F43">
-        <v>3.52436</v>
+        <v>3.61032</v>
       </c>
       <c r="G43">
         <v>0.16</v>
@@ -4813,28 +4813,28 @@
         <v>0.715</v>
       </c>
       <c r="M43">
-        <v>0.225911476</v>
+        <v>0.231421512</v>
       </c>
       <c r="N43">
-        <v>0.4890885239999999</v>
+        <v>0.4835784879999999</v>
       </c>
       <c r="O43">
-        <v>0.07336327859999998</v>
+        <v>0.07253677319999999</v>
       </c>
       <c r="P43">
-        <v>0.4157252453999999</v>
+        <v>0.4110417148</v>
       </c>
       <c r="Q43">
-        <v>0.6747252453999999</v>
+        <v>0.6700417148</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1286120709904058</v>
+        <v>0.1299052251494976</v>
       </c>
       <c r="T43">
-        <v>1.516732162587365</v>
+        <v>1.540416735148114</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.164956524829221</v>
+        <v>3.089600417095192</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09822873058670864</v>
+        <v>0.09823748928907786</v>
       </c>
       <c r="C44">
-        <v>4.930251437787737</v>
+        <v>4.842891619987482</v>
       </c>
       <c r="D44">
-        <v>8.380571437787736</v>
+        <v>8.379171619987481</v>
       </c>
       <c r="E44">
-        <v>3.53432</v>
+        <v>3.62028</v>
       </c>
       <c r="F44">
-        <v>3.61032</v>
+        <v>3.69628</v>
       </c>
       <c r="G44">
         <v>0.16</v>
@@ -4895,28 +4895,28 @@
         <v>0.715</v>
       </c>
       <c r="M44">
-        <v>0.231421512</v>
+        <v>0.236931548</v>
       </c>
       <c r="N44">
-        <v>0.483578488</v>
+        <v>0.478068452</v>
       </c>
       <c r="O44">
-        <v>0.07253677319999999</v>
+        <v>0.07171026779999999</v>
       </c>
       <c r="P44">
-        <v>0.4110417148</v>
+        <v>0.4063581842</v>
       </c>
       <c r="Q44">
-        <v>0.6700417148</v>
+        <v>0.6653581842</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1299052251494976</v>
+        <v>0.131243753138733</v>
       </c>
       <c r="T44">
-        <v>1.540416735148114</v>
+        <v>1.564932345342574</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.089600417095192</v>
+        <v>3.017749244604606</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09823748928907786</v>
+        <v>0.101163447991447</v>
       </c>
       <c r="C45">
-        <v>4.842891619987482</v>
+        <v>4.314092327826074</v>
       </c>
       <c r="D45">
-        <v>8.379171619987481</v>
+        <v>7.936332327826074</v>
       </c>
       <c r="E45">
-        <v>3.62028</v>
+        <v>3.70624</v>
       </c>
       <c r="F45">
-        <v>3.69628</v>
+        <v>3.78224</v>
       </c>
       <c r="G45">
         <v>0.16</v>
@@ -4977,45 +4977,45 @@
         <v>0.715</v>
       </c>
       <c r="M45">
-        <v>0.236931548</v>
+        <v>0.271943056</v>
       </c>
       <c r="N45">
-        <v>0.478068452</v>
+        <v>0.443056944</v>
       </c>
       <c r="O45">
-        <v>0.07171026779999999</v>
+        <v>0.06645854159999999</v>
       </c>
       <c r="P45">
-        <v>0.4063581842</v>
+        <v>0.3765984024</v>
       </c>
       <c r="Q45">
-        <v>0.6653581842</v>
+        <v>0.6355984024</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.131243753138733</v>
+        <v>0.1326300856990126</v>
       </c>
       <c r="T45">
-        <v>1.564932345342574</v>
+        <v>1.590323513043978</v>
       </c>
       <c r="U45">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V45">
         <v>0.15</v>
       </c>
       <c r="W45">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.017749244604606</v>
+        <v>2.62922690697423</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.101163447991447</v>
+        <v>0.1012385066938162</v>
       </c>
       <c r="C46">
-        <v>4.314092327826074</v>
+        <v>4.217387254741995</v>
       </c>
       <c r="D46">
-        <v>7.936332327826074</v>
+        <v>7.925587254741995</v>
       </c>
       <c r="E46">
-        <v>3.70624</v>
+        <v>3.7922</v>
       </c>
       <c r="F46">
-        <v>3.78224</v>
+        <v>3.8682</v>
       </c>
       <c r="G46">
         <v>0.16</v>
@@ -5059,28 +5059,28 @@
         <v>0.715</v>
       </c>
       <c r="M46">
-        <v>0.271943056</v>
+        <v>0.27812358</v>
       </c>
       <c r="N46">
-        <v>0.443056944</v>
+        <v>0.4368764199999999</v>
       </c>
       <c r="O46">
-        <v>0.06645854159999999</v>
+        <v>0.06553146299999998</v>
       </c>
       <c r="P46">
-        <v>0.3765984024</v>
+        <v>0.3713449569999999</v>
       </c>
       <c r="Q46">
-        <v>0.6355984024</v>
+        <v>0.6303449569999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1326300856990126</v>
+        <v>0.1340668303523931</v>
       </c>
       <c r="T46">
-        <v>1.590323513043978</v>
+        <v>1.616637995934525</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.62922690697423</v>
+        <v>2.570799642374803</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1012385066938162</v>
+        <v>0.1013135653961854</v>
       </c>
       <c r="C47">
-        <v>4.217387254741995</v>
+        <v>4.120711238024111</v>
       </c>
       <c r="D47">
-        <v>7.925587254741995</v>
+        <v>7.914871238024111</v>
       </c>
       <c r="E47">
-        <v>3.7922</v>
+        <v>3.87816</v>
       </c>
       <c r="F47">
-        <v>3.8682</v>
+        <v>3.95416</v>
       </c>
       <c r="G47">
         <v>0.16</v>
@@ -5141,28 +5141,28 @@
         <v>0.715</v>
       </c>
       <c r="M47">
-        <v>0.27812358</v>
+        <v>0.2843041040000001</v>
       </c>
       <c r="N47">
-        <v>0.4368764199999999</v>
+        <v>0.4306958959999999</v>
       </c>
       <c r="O47">
-        <v>0.06553146299999998</v>
+        <v>0.06460438439999998</v>
       </c>
       <c r="P47">
-        <v>0.3713449569999999</v>
+        <v>0.3660915115999999</v>
       </c>
       <c r="Q47">
-        <v>0.6303449569999999</v>
+        <v>0.6250915116</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1340668303523931</v>
+        <v>0.1355567877707138</v>
       </c>
       <c r="T47">
-        <v>1.616637995934525</v>
+        <v>1.643927089302499</v>
       </c>
       <c r="U47">
         <v>0.07190000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.570799642374803</v>
+        <v>2.514912693627524</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1013135653961854</v>
+        <v>0.1029466740985546</v>
       </c>
       <c r="C48">
-        <v>4.120711238024111</v>
+        <v>3.808564057390345</v>
       </c>
       <c r="D48">
-        <v>7.914871238024111</v>
+        <v>7.688684057390345</v>
       </c>
       <c r="E48">
-        <v>3.87816</v>
+        <v>3.96412</v>
       </c>
       <c r="F48">
-        <v>3.95416</v>
+        <v>4.04012</v>
       </c>
       <c r="G48">
         <v>0.16</v>
@@ -5223,45 +5223,45 @@
         <v>0.715</v>
       </c>
       <c r="M48">
-        <v>0.2843041040000001</v>
+        <v>0.306241096</v>
       </c>
       <c r="N48">
-        <v>0.4306958959999999</v>
+        <v>0.4087589039999999</v>
       </c>
       <c r="O48">
-        <v>0.06460438439999998</v>
+        <v>0.06131383559999998</v>
       </c>
       <c r="P48">
-        <v>0.3660915115999999</v>
+        <v>0.3474450683999999</v>
       </c>
       <c r="Q48">
-        <v>0.6250915116</v>
+        <v>0.6064450684</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1355567877707138</v>
+        <v>0.1371029699972729</v>
       </c>
       <c r="T48">
-        <v>1.643927089302499</v>
+        <v>1.672245959778699</v>
       </c>
       <c r="U48">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V48">
         <v>0.15</v>
       </c>
       <c r="W48">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.514912693627524</v>
+        <v>2.334761759081478</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1029466740985546</v>
+        <v>0.1030548828009238</v>
       </c>
       <c r="C49">
-        <v>3.808564057390345</v>
+        <v>3.708072850896223</v>
       </c>
       <c r="D49">
-        <v>7.688684057390345</v>
+        <v>7.674152850896223</v>
       </c>
       <c r="E49">
-        <v>3.96412</v>
+        <v>4.05008</v>
       </c>
       <c r="F49">
-        <v>4.04012</v>
+        <v>4.12608</v>
       </c>
       <c r="G49">
         <v>0.16</v>
@@ -5305,28 +5305,28 @@
         <v>0.715</v>
       </c>
       <c r="M49">
-        <v>0.306241096</v>
+        <v>0.312756864</v>
       </c>
       <c r="N49">
-        <v>0.4087589039999999</v>
+        <v>0.4022431359999999</v>
       </c>
       <c r="O49">
-        <v>0.06131383559999998</v>
+        <v>0.06033647039999999</v>
       </c>
       <c r="P49">
-        <v>0.3474450683999999</v>
+        <v>0.3419066655999999</v>
       </c>
       <c r="Q49">
-        <v>0.6064450684</v>
+        <v>0.6009066655999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1371029699972729</v>
+        <v>0.1387086207710073</v>
       </c>
       <c r="T49">
-        <v>1.672245959778699</v>
+        <v>1.701654017580906</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.334761759081478</v>
+        <v>2.286120889100614</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1030548828009238</v>
+        <v>0.103163091503293</v>
       </c>
       <c r="C50">
-        <v>3.708072850896225</v>
+        <v>3.607636467214382</v>
       </c>
       <c r="D50">
-        <v>7.674152850896225</v>
+        <v>7.659676467214382</v>
       </c>
       <c r="E50">
-        <v>4.05008</v>
+        <v>4.13604</v>
       </c>
       <c r="F50">
-        <v>4.12608</v>
+        <v>4.21204</v>
       </c>
       <c r="G50">
         <v>0.16</v>
@@ -5387,28 +5387,28 @@
         <v>0.715</v>
       </c>
       <c r="M50">
-        <v>0.312756864</v>
+        <v>0.319272632</v>
       </c>
       <c r="N50">
-        <v>0.4022431359999999</v>
+        <v>0.395727368</v>
       </c>
       <c r="O50">
-        <v>0.06033647039999999</v>
+        <v>0.05935910519999999</v>
       </c>
       <c r="P50">
-        <v>0.3419066655999999</v>
+        <v>0.3363682628</v>
       </c>
       <c r="Q50">
-        <v>0.6009066655999999</v>
+        <v>0.5953682628</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1387086207710073</v>
+        <v>0.140377238241751</v>
       </c>
       <c r="T50">
-        <v>1.701654017580906</v>
+        <v>1.732215332551828</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.286120889100614</v>
+        <v>2.239465360751622</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.103163091503293</v>
+        <v>0.1032713002056622</v>
       </c>
       <c r="C51">
-        <v>3.607636467214382</v>
+        <v>3.507254596678667</v>
       </c>
       <c r="D51">
-        <v>7.659676467214382</v>
+        <v>7.645254596678667</v>
       </c>
       <c r="E51">
-        <v>4.13604</v>
+        <v>4.222</v>
       </c>
       <c r="F51">
-        <v>4.21204</v>
+        <v>4.298</v>
       </c>
       <c r="G51">
         <v>0.16</v>
@@ -5469,28 +5469,28 @@
         <v>0.715</v>
       </c>
       <c r="M51">
-        <v>0.319272632</v>
+        <v>0.3257884</v>
       </c>
       <c r="N51">
-        <v>0.395727368</v>
+        <v>0.3892115999999999</v>
       </c>
       <c r="O51">
-        <v>0.05935910519999999</v>
+        <v>0.05838173999999999</v>
       </c>
       <c r="P51">
-        <v>0.3363682628</v>
+        <v>0.3308298599999999</v>
       </c>
       <c r="Q51">
-        <v>0.5953682628</v>
+        <v>0.5898298599999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.140377238241751</v>
+        <v>0.1421126004113244</v>
       </c>
       <c r="T51">
-        <v>1.732215332551828</v>
+        <v>1.763999100121586</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.239465360751622</v>
+        <v>2.19467605353659</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1032713002056622</v>
+        <v>0.1033795089080314</v>
       </c>
       <c r="C52">
-        <v>3.507254596678667</v>
+        <v>3.406926931950747</v>
       </c>
       <c r="D52">
-        <v>7.645254596678667</v>
+        <v>7.630886931950747</v>
       </c>
       <c r="E52">
-        <v>4.222</v>
+        <v>4.30796</v>
       </c>
       <c r="F52">
-        <v>4.298</v>
+        <v>4.38396</v>
       </c>
       <c r="G52">
         <v>0.16</v>
@@ -5551,28 +5551,28 @@
         <v>0.715</v>
       </c>
       <c r="M52">
-        <v>0.3257884</v>
+        <v>0.332304168</v>
       </c>
       <c r="N52">
-        <v>0.3892115999999999</v>
+        <v>0.382695832</v>
       </c>
       <c r="O52">
-        <v>0.05838173999999999</v>
+        <v>0.05740437479999999</v>
       </c>
       <c r="P52">
-        <v>0.3308298599999999</v>
+        <v>0.3252914572</v>
       </c>
       <c r="Q52">
-        <v>0.5898298599999999</v>
+        <v>0.5842914572</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1421126004113244</v>
+        <v>0.14391879368986</v>
       </c>
       <c r="T52">
-        <v>1.763999100121586</v>
+        <v>1.797080164326845</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.19467605353659</v>
+        <v>2.151643189741755</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1033795089080314</v>
+        <v>0.1034877176104006</v>
       </c>
       <c r="C53">
-        <v>3.406926931950747</v>
+        <v>3.306653167998274</v>
       </c>
       <c r="D53">
-        <v>7.630886931950747</v>
+        <v>7.616573167998274</v>
       </c>
       <c r="E53">
-        <v>4.30796</v>
+        <v>4.39392</v>
       </c>
       <c r="F53">
-        <v>4.38396</v>
+        <v>4.46992</v>
       </c>
       <c r="G53">
         <v>0.16</v>
@@ -5633,28 +5633,28 @@
         <v>0.715</v>
       </c>
       <c r="M53">
-        <v>0.332304168</v>
+        <v>0.338819936</v>
       </c>
       <c r="N53">
-        <v>0.382695832</v>
+        <v>0.3761800639999999</v>
       </c>
       <c r="O53">
-        <v>0.05740437479999999</v>
+        <v>0.05642700959999999</v>
       </c>
       <c r="P53">
-        <v>0.3252914572</v>
+        <v>0.3197530544</v>
       </c>
       <c r="Q53">
-        <v>0.5842914572</v>
+        <v>0.5787530543999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.14391879368986</v>
+        <v>0.1458002450216679</v>
       </c>
       <c r="T53">
-        <v>1.797080164326845</v>
+        <v>1.831539606207323</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.151643189741755</v>
+        <v>2.110265436092875</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1034877176104006</v>
+        <v>0.1035959263127698</v>
       </c>
       <c r="C54">
-        <v>3.306653167998274</v>
+        <v>3.206433002073272</v>
       </c>
       <c r="D54">
-        <v>7.616573167998274</v>
+        <v>7.602313002073272</v>
       </c>
       <c r="E54">
-        <v>4.39392</v>
+        <v>4.479880000000001</v>
       </c>
       <c r="F54">
-        <v>4.46992</v>
+        <v>4.55588</v>
       </c>
       <c r="G54">
         <v>0.16</v>
@@ -5715,28 +5715,28 @@
         <v>0.715</v>
       </c>
       <c r="M54">
-        <v>0.338819936</v>
+        <v>0.345335704</v>
       </c>
       <c r="N54">
-        <v>0.3761800639999999</v>
+        <v>0.3696642959999999</v>
       </c>
       <c r="O54">
-        <v>0.05642700959999999</v>
+        <v>0.05544964439999999</v>
       </c>
       <c r="P54">
-        <v>0.3197530544</v>
+        <v>0.3142146516</v>
       </c>
       <c r="Q54">
-        <v>0.5787530543999999</v>
+        <v>0.5732146516</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1458002450216679</v>
+        <v>0.1477617581122762</v>
       </c>
       <c r="T54">
-        <v>1.831539606207323</v>
+        <v>1.867465407316757</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.110265436092875</v>
+        <v>2.07044910710999</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1035959263127698</v>
+        <v>0.103704135015139</v>
       </c>
       <c r="C55">
-        <v>3.206433002073272</v>
+        <v>3.106266133690838</v>
       </c>
       <c r="D55">
-        <v>7.602313002073272</v>
+        <v>7.588106133690838</v>
       </c>
       <c r="E55">
-        <v>4.479880000000001</v>
+        <v>4.565840000000001</v>
       </c>
       <c r="F55">
-        <v>4.55588</v>
+        <v>4.64184</v>
       </c>
       <c r="G55">
         <v>0.16</v>
@@ -5797,28 +5797,28 @@
         <v>0.715</v>
       </c>
       <c r="M55">
-        <v>0.345335704</v>
+        <v>0.3518514720000001</v>
       </c>
       <c r="N55">
-        <v>0.3696642959999999</v>
+        <v>0.3631485279999999</v>
       </c>
       <c r="O55">
-        <v>0.05544964439999999</v>
+        <v>0.05447227919999999</v>
       </c>
       <c r="P55">
-        <v>0.3142146516</v>
+        <v>0.3086762487999999</v>
       </c>
       <c r="Q55">
-        <v>0.5732146516</v>
+        <v>0.5676762488</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1477617581122762</v>
+        <v>0.149808554380737</v>
       </c>
       <c r="T55">
-        <v>1.867465407316757</v>
+        <v>1.904953199778775</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.07044910710999</v>
+        <v>2.032107456978324</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.103704135015139</v>
+        <v>0.1104508437175082</v>
       </c>
       <c r="C56">
-        <v>3.106266133690838</v>
+        <v>2.228441113175895</v>
       </c>
       <c r="D56">
-        <v>7.588106133690838</v>
+        <v>6.796241113175895</v>
       </c>
       <c r="E56">
-        <v>4.565840000000001</v>
+        <v>4.651800000000001</v>
       </c>
       <c r="F56">
-        <v>4.64184</v>
+        <v>4.7278</v>
       </c>
       <c r="G56">
         <v>0.16</v>
@@ -5879,45 +5879,45 @@
         <v>0.715</v>
       </c>
       <c r="M56">
-        <v>0.3518514720000001</v>
+        <v>0.425502</v>
       </c>
       <c r="N56">
-        <v>0.3631485279999999</v>
+        <v>0.289498</v>
       </c>
       <c r="O56">
-        <v>0.05447227919999999</v>
+        <v>0.0434247</v>
       </c>
       <c r="P56">
-        <v>0.3086762487999999</v>
+        <v>0.2460733</v>
       </c>
       <c r="Q56">
-        <v>0.5676762488</v>
+        <v>0.5050733000000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.149808554380737</v>
+        <v>0.1519463193722405</v>
       </c>
       <c r="T56">
-        <v>1.904953199778775</v>
+        <v>1.944107116350217</v>
       </c>
       <c r="U56">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V56">
         <v>0.15</v>
       </c>
       <c r="W56">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.032107456978324</v>
+        <v>1.68036812987953</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1104508437175082</v>
+        <v>0.1106797524198774</v>
       </c>
       <c r="C57">
-        <v>2.228441113175895</v>
+        <v>2.118502619482866</v>
       </c>
       <c r="D57">
-        <v>6.796241113175895</v>
+        <v>6.772262619482866</v>
       </c>
       <c r="E57">
-        <v>4.651800000000001</v>
+        <v>4.737760000000001</v>
       </c>
       <c r="F57">
-        <v>4.7278</v>
+        <v>4.81376</v>
       </c>
       <c r="G57">
         <v>0.16</v>
@@ -5961,28 +5961,28 @@
         <v>0.715</v>
       </c>
       <c r="M57">
-        <v>0.425502</v>
+        <v>0.4332384</v>
       </c>
       <c r="N57">
-        <v>0.289498</v>
+        <v>0.2817615999999999</v>
       </c>
       <c r="O57">
-        <v>0.0434247</v>
+        <v>0.04226423999999999</v>
       </c>
       <c r="P57">
-        <v>0.2460733</v>
+        <v>0.23949736</v>
       </c>
       <c r="Q57">
-        <v>0.5050733000000001</v>
+        <v>0.49849736</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1519463193722405</v>
+        <v>0.1541812554997214</v>
       </c>
       <c r="T57">
-        <v>1.944107116350217</v>
+        <v>1.985040756402178</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.68036812987953</v>
+        <v>1.650361556131682</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1106797524198774</v>
+        <v>0.1109086611222466</v>
       </c>
       <c r="C58">
-        <v>2.118502619482866</v>
+        <v>2.008732732724197</v>
       </c>
       <c r="D58">
-        <v>6.772262619482866</v>
+        <v>6.748452732724197</v>
       </c>
       <c r="E58">
-        <v>4.737760000000001</v>
+        <v>4.823720000000001</v>
       </c>
       <c r="F58">
-        <v>4.81376</v>
+        <v>4.89972</v>
       </c>
       <c r="G58">
         <v>0.16</v>
@@ -6043,28 +6043,28 @@
         <v>0.715</v>
       </c>
       <c r="M58">
-        <v>0.4332384</v>
+        <v>0.4409748</v>
       </c>
       <c r="N58">
-        <v>0.2817615999999999</v>
+        <v>0.2740252</v>
       </c>
       <c r="O58">
-        <v>0.04226423999999999</v>
+        <v>0.04110377999999999</v>
       </c>
       <c r="P58">
-        <v>0.23949736</v>
+        <v>0.23292142</v>
       </c>
       <c r="Q58">
-        <v>0.49849736</v>
+        <v>0.49192142</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1541812554997214</v>
+        <v>0.1565201421447595</v>
       </c>
       <c r="T58">
-        <v>1.985040756402178</v>
+        <v>2.027878286689115</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.650361556131682</v>
+        <v>1.6214078446206</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1109086611222466</v>
+        <v>0.1111375698246158</v>
       </c>
       <c r="C59">
-        <v>2.008732732724197</v>
+        <v>1.899129680768112</v>
       </c>
       <c r="D59">
-        <v>6.748452732724197</v>
+        <v>6.724809680768112</v>
       </c>
       <c r="E59">
-        <v>4.823720000000001</v>
+        <v>4.909680000000001</v>
       </c>
       <c r="F59">
-        <v>4.89972</v>
+        <v>4.98568</v>
       </c>
       <c r="G59">
         <v>0.16</v>
@@ -6125,28 +6125,28 @@
         <v>0.715</v>
       </c>
       <c r="M59">
-        <v>0.4409748</v>
+        <v>0.4487112</v>
       </c>
       <c r="N59">
-        <v>0.2740252</v>
+        <v>0.2662887999999999</v>
       </c>
       <c r="O59">
-        <v>0.04110377999999999</v>
+        <v>0.03994331999999999</v>
       </c>
       <c r="P59">
-        <v>0.23292142</v>
+        <v>0.2263454799999999</v>
       </c>
       <c r="Q59">
-        <v>0.49192142</v>
+        <v>0.4853454799999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1565201421447595</v>
+        <v>0.1589704043443233</v>
       </c>
       <c r="T59">
-        <v>2.027878286689115</v>
+        <v>2.072755699370667</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.6214078446206</v>
+        <v>1.593452536954727</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1111375698246158</v>
+        <v>0.111366478526985</v>
       </c>
       <c r="C60">
-        <v>1.899129680768114</v>
+        <v>1.789691716230626</v>
       </c>
       <c r="D60">
-        <v>6.724809680768113</v>
+        <v>6.701331716230626</v>
       </c>
       <c r="E60">
-        <v>4.90968</v>
+        <v>4.99564</v>
       </c>
       <c r="F60">
-        <v>4.985679999999999</v>
+        <v>5.071639999999999</v>
       </c>
       <c r="G60">
         <v>0.16</v>
@@ -6207,28 +6207,28 @@
         <v>0.715</v>
       </c>
       <c r="M60">
-        <v>0.4487111999999999</v>
+        <v>0.4564476</v>
       </c>
       <c r="N60">
-        <v>0.2662888</v>
+        <v>0.2585524</v>
       </c>
       <c r="O60">
-        <v>0.03994332</v>
+        <v>0.03878286</v>
       </c>
       <c r="P60">
-        <v>0.22634548</v>
+        <v>0.21976954</v>
       </c>
       <c r="Q60">
-        <v>0.4853454800000001</v>
+        <v>0.47876954</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1589704043443233</v>
+        <v>0.1615401915292316</v>
       </c>
       <c r="T60">
-        <v>2.072755699370667</v>
+        <v>2.119822254134246</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.593452536954727</v>
+        <v>1.56644486683685</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.111366478526985</v>
+        <v>0.1115953872293542</v>
       </c>
       <c r="C61">
-        <v>1.789691716230626</v>
+        <v>1.680417116045044</v>
       </c>
       <c r="D61">
-        <v>6.701331716230626</v>
+        <v>6.678017116045043</v>
       </c>
       <c r="E61">
-        <v>4.99564</v>
+        <v>5.0816</v>
       </c>
       <c r="F61">
-        <v>5.071639999999999</v>
+        <v>5.1576</v>
       </c>
       <c r="G61">
         <v>0.16</v>
@@ -6289,28 +6289,28 @@
         <v>0.715</v>
       </c>
       <c r="M61">
-        <v>0.4564476</v>
+        <v>0.4641839999999999</v>
       </c>
       <c r="N61">
-        <v>0.2585524</v>
+        <v>0.250816</v>
       </c>
       <c r="O61">
-        <v>0.03878286</v>
+        <v>0.03762240000000001</v>
       </c>
       <c r="P61">
-        <v>0.21976954</v>
+        <v>0.2131936</v>
       </c>
       <c r="Q61">
-        <v>0.47876954</v>
+        <v>0.4721936</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1615401915292316</v>
+        <v>0.1642384680733854</v>
       </c>
       <c r="T61">
-        <v>2.119822254134246</v>
+        <v>2.169242136636004</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.56644486683685</v>
+        <v>1.54033745238957</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1115953872293542</v>
+        <v>0.1118242959317234</v>
       </c>
       <c r="C62">
-        <v>1.680417116045044</v>
+        <v>1.571304181040423</v>
       </c>
       <c r="D62">
-        <v>6.678017116045043</v>
+        <v>6.654864181040423</v>
       </c>
       <c r="E62">
-        <v>5.0816</v>
+        <v>5.16756</v>
       </c>
       <c r="F62">
-        <v>5.1576</v>
+        <v>5.24356</v>
       </c>
       <c r="G62">
         <v>0.16</v>
@@ -6371,28 +6371,28 @@
         <v>0.715</v>
       </c>
       <c r="M62">
-        <v>0.4641839999999999</v>
+        <v>0.4719204</v>
       </c>
       <c r="N62">
-        <v>0.250816</v>
+        <v>0.2430796</v>
       </c>
       <c r="O62">
-        <v>0.03762240000000001</v>
+        <v>0.03646194</v>
       </c>
       <c r="P62">
-        <v>0.2131936</v>
+        <v>0.20661766</v>
       </c>
       <c r="Q62">
-        <v>0.4721936</v>
+        <v>0.46561766</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1642384680733854</v>
+        <v>0.1670751177736497</v>
       </c>
       <c r="T62">
-        <v>2.169242136636004</v>
+        <v>2.221196372086571</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.54033745238957</v>
+        <v>1.515086018743839</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1118242959317234</v>
+        <v>0.1435794073876241</v>
       </c>
       <c r="C63">
-        <v>1.571304181040423</v>
+        <v>-0.6759079623180115</v>
       </c>
       <c r="D63">
-        <v>6.654864181040423</v>
+        <v>4.493612037681988</v>
       </c>
       <c r="E63">
-        <v>5.16756</v>
+        <v>5.25352</v>
       </c>
       <c r="F63">
-        <v>5.24356</v>
+        <v>5.32952</v>
       </c>
       <c r="G63">
         <v>0.16</v>
@@ -6453,45 +6453,45 @@
         <v>0.715</v>
       </c>
       <c r="M63">
-        <v>0.4719204</v>
+        <v>0.782373536</v>
       </c>
       <c r="N63">
-        <v>0.2430796</v>
+        <v>-0.06737353600000007</v>
       </c>
       <c r="O63">
-        <v>0.03646194</v>
+        <v>-0.01010603040000001</v>
       </c>
       <c r="P63">
-        <v>0.20661766</v>
+        <v>-0.05726750560000006</v>
       </c>
       <c r="Q63">
-        <v>0.46561766</v>
+        <v>0.2017324944</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1670751177736497</v>
+        <v>0.1711582651367884</v>
       </c>
       <c r="T63">
-        <v>2.221196372086571</v>
+        <v>2.295980649984581</v>
       </c>
       <c r="U63">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.15</v>
+        <v>0.1370828575674114</v>
       </c>
       <c r="W63">
-        <v>0.0765</v>
+        <v>0.126676236509104</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>1.515086018743839</v>
+        <v>0.9138857171160758</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1435794073876241</v>
+        <v>0.1445894073876241</v>
       </c>
       <c r="C64">
-        <v>-0.6759079623180115</v>
+        <v>-0.8078096100925629</v>
       </c>
       <c r="D64">
-        <v>4.493612037681988</v>
+        <v>4.447670389907437</v>
       </c>
       <c r="E64">
-        <v>5.25352</v>
+        <v>5.339480000000001</v>
       </c>
       <c r="F64">
-        <v>5.32952</v>
+        <v>5.415480000000001</v>
       </c>
       <c r="G64">
         <v>0.16</v>
@@ -6535,37 +6535,37 @@
         <v>0.715</v>
       </c>
       <c r="M64">
-        <v>0.782373536</v>
+        <v>0.7949924640000001</v>
       </c>
       <c r="N64">
-        <v>-0.06737353600000007</v>
+        <v>-0.07999246400000015</v>
       </c>
       <c r="O64">
-        <v>-0.01010603040000001</v>
+        <v>-0.01199886960000002</v>
       </c>
       <c r="P64">
-        <v>-0.05726750560000006</v>
+        <v>-0.06799359440000013</v>
       </c>
       <c r="Q64">
-        <v>0.2017324944</v>
+        <v>0.1910064055999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1711582651367884</v>
+        <v>0.1745463263567016</v>
       </c>
       <c r="T64">
-        <v>2.295980649984581</v>
+        <v>2.358034181065245</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1370828575674114</v>
+        <v>0.1349069391933255</v>
       </c>
       <c r="W64">
-        <v>0.126676236509104</v>
+        <v>0.1269956613264198</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.9138857171160758</v>
+        <v>0.8993795946221698</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1445894073876241</v>
+        <v>0.1455994073876241</v>
       </c>
       <c r="C65">
-        <v>-0.8078096100925629</v>
+        <v>-0.9387813712983064</v>
       </c>
       <c r="D65">
-        <v>4.447670389907437</v>
+        <v>4.402658628701694</v>
       </c>
       <c r="E65">
-        <v>5.339480000000001</v>
+        <v>5.425440000000001</v>
       </c>
       <c r="F65">
-        <v>5.415480000000001</v>
+        <v>5.501440000000001</v>
       </c>
       <c r="G65">
         <v>0.16</v>
@@ -6617,37 +6617,37 @@
         <v>0.715</v>
       </c>
       <c r="M65">
-        <v>0.7949924640000001</v>
+        <v>0.8076113920000002</v>
       </c>
       <c r="N65">
-        <v>-0.07999246400000015</v>
+        <v>-0.09261139200000024</v>
       </c>
       <c r="O65">
-        <v>-0.01199886960000002</v>
+        <v>-0.01389170880000004</v>
       </c>
       <c r="P65">
-        <v>-0.06799359440000013</v>
+        <v>-0.0787196832000002</v>
       </c>
       <c r="Q65">
-        <v>0.1910064055999999</v>
+        <v>0.1802803167999998</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1745463263567016</v>
+        <v>0.1781226131999433</v>
       </c>
       <c r="T65">
-        <v>2.358034181065245</v>
+        <v>2.42353513053928</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1349069391933255</v>
+        <v>0.1327990182684297</v>
       </c>
       <c r="W65">
-        <v>0.1269956613264198</v>
+        <v>0.1273051041181945</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8993795946221698</v>
+        <v>0.8853267884561983</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1455994073876241</v>
+        <v>0.1466094073876241</v>
       </c>
       <c r="C66">
-        <v>-0.9387813712983064</v>
+        <v>-1.068851195274265</v>
       </c>
       <c r="D66">
-        <v>4.402658628701694</v>
+        <v>4.358548804725736</v>
       </c>
       <c r="E66">
-        <v>5.425440000000001</v>
+        <v>5.511400000000001</v>
       </c>
       <c r="F66">
-        <v>5.501440000000001</v>
+        <v>5.587400000000001</v>
       </c>
       <c r="G66">
         <v>0.16</v>
@@ -6699,37 +6699,37 @@
         <v>0.715</v>
       </c>
       <c r="M66">
-        <v>0.8076113920000002</v>
+        <v>0.8202303200000002</v>
       </c>
       <c r="N66">
-        <v>-0.09261139200000024</v>
+        <v>-0.1052303200000002</v>
       </c>
       <c r="O66">
-        <v>-0.01389170880000004</v>
+        <v>-0.01578454800000003</v>
       </c>
       <c r="P66">
-        <v>-0.0787196832000002</v>
+        <v>-0.08944577200000017</v>
       </c>
       <c r="Q66">
-        <v>0.1802803167999998</v>
+        <v>0.1695542279999998</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1781226131999433</v>
+        <v>0.1819032592913702</v>
       </c>
       <c r="T66">
-        <v>2.42353513053928</v>
+        <v>2.492778991411831</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1327990182684297</v>
+        <v>0.1307559564489154</v>
       </c>
       <c r="W66">
-        <v>0.1273051041181945</v>
+        <v>0.1276050255932992</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8853267884561983</v>
+        <v>0.8717063763261029</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1466094073876241</v>
+        <v>0.1476194073876241</v>
       </c>
       <c r="C67">
-        <v>-1.068851195274265</v>
+        <v>-1.19804592238296</v>
       </c>
       <c r="D67">
-        <v>4.358548804725736</v>
+        <v>4.315314077617041</v>
       </c>
       <c r="E67">
-        <v>5.511400000000001</v>
+        <v>5.597360000000001</v>
       </c>
       <c r="F67">
-        <v>5.587400000000001</v>
+        <v>5.673360000000001</v>
       </c>
       <c r="G67">
         <v>0.16</v>
@@ -6781,37 +6781,37 @@
         <v>0.715</v>
       </c>
       <c r="M67">
-        <v>0.8202303200000002</v>
+        <v>0.8328492480000002</v>
       </c>
       <c r="N67">
-        <v>-0.1052303200000002</v>
+        <v>-0.1178492480000002</v>
       </c>
       <c r="O67">
-        <v>-0.01578454800000003</v>
+        <v>-0.01767738720000003</v>
       </c>
       <c r="P67">
-        <v>-0.08944577200000017</v>
+        <v>-0.1001718608000002</v>
       </c>
       <c r="Q67">
-        <v>0.1695542279999998</v>
+        <v>0.1588281391999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1819032592913702</v>
+        <v>0.1859062963293517</v>
       </c>
       <c r="T67">
-        <v>2.492778991411831</v>
+        <v>2.566096020571003</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.1307559564489154</v>
+        <v>0.1287748055936288</v>
       </c>
       <c r="W67">
-        <v>0.1276050255932992</v>
+        <v>0.1278958585388553</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8717063763261029</v>
+        <v>0.8584987039575256</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1476194073876241</v>
+        <v>0.1486294073876241</v>
       </c>
       <c r="C68">
-        <v>-1.19804592238296</v>
+        <v>-1.326391338472772</v>
       </c>
       <c r="D68">
-        <v>4.315314077617041</v>
+        <v>4.272928661527229</v>
       </c>
       <c r="E68">
-        <v>5.597360000000001</v>
+        <v>5.683320000000001</v>
       </c>
       <c r="F68">
-        <v>5.673360000000001</v>
+        <v>5.759320000000001</v>
       </c>
       <c r="G68">
         <v>0.16</v>
@@ -6863,37 +6863,37 @@
         <v>0.715</v>
       </c>
       <c r="M68">
-        <v>0.8328492480000002</v>
+        <v>0.8454681760000001</v>
       </c>
       <c r="N68">
-        <v>-0.1178492480000002</v>
+        <v>-0.1304681760000002</v>
       </c>
       <c r="O68">
-        <v>-0.01767738720000003</v>
+        <v>-0.01957022640000002</v>
       </c>
       <c r="P68">
-        <v>-0.1001718608000002</v>
+        <v>-0.1108979496000001</v>
       </c>
       <c r="Q68">
-        <v>0.1588281391999999</v>
+        <v>0.1481020503999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1859062963293517</v>
+        <v>0.1901519416726654</v>
       </c>
       <c r="T68">
-        <v>2.566096020571003</v>
+        <v>2.643856506042851</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1287748055936288</v>
+        <v>0.1268527935698433</v>
       </c>
       <c r="W68">
-        <v>0.1278958585388553</v>
+        <v>0.128178009903947</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8584987039575256</v>
+        <v>0.8456852904656222</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1486294073876241</v>
+        <v>0.1496394073876241</v>
       </c>
       <c r="C69">
-        <v>-1.326391338472772</v>
+        <v>-1.453912226161899</v>
       </c>
       <c r="D69">
-        <v>4.272928661527229</v>
+        <v>4.231367773838102</v>
       </c>
       <c r="E69">
-        <v>5.683320000000001</v>
+        <v>5.769280000000001</v>
       </c>
       <c r="F69">
-        <v>5.759320000000001</v>
+        <v>5.845280000000001</v>
       </c>
       <c r="G69">
         <v>0.16</v>
@@ -6945,37 +6945,37 @@
         <v>0.715</v>
       </c>
       <c r="M69">
-        <v>0.8454681760000001</v>
+        <v>0.8580871040000002</v>
       </c>
       <c r="N69">
-        <v>-0.1304681760000002</v>
+        <v>-0.1430871040000002</v>
       </c>
       <c r="O69">
-        <v>-0.01957022640000002</v>
+        <v>-0.02146306560000004</v>
       </c>
       <c r="P69">
-        <v>-0.1108979496000001</v>
+        <v>-0.1216240384000002</v>
       </c>
       <c r="Q69">
-        <v>0.1481020503999999</v>
+        <v>0.1373759615999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1901519416726654</v>
+        <v>0.1946629398499362</v>
       </c>
       <c r="T69">
-        <v>2.643856506042851</v>
+        <v>2.726477021856691</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.1268527935698433</v>
+        <v>0.1249873113114633</v>
       </c>
       <c r="W69">
-        <v>0.128178009903947</v>
+        <v>0.1284518626994772</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8456852904656222</v>
+        <v>0.8332487420764219</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1496394073876241</v>
+        <v>0.1506494073876241</v>
       </c>
       <c r="C70">
-        <v>-1.453912226161899</v>
+        <v>-1.580632413158255</v>
       </c>
       <c r="D70">
-        <v>4.231367773838102</v>
+        <v>4.190607586841746</v>
       </c>
       <c r="E70">
-        <v>5.769280000000001</v>
+        <v>5.855240000000001</v>
       </c>
       <c r="F70">
-        <v>5.845280000000001</v>
+        <v>5.931240000000001</v>
       </c>
       <c r="G70">
         <v>0.16</v>
@@ -7027,37 +7027,37 @@
         <v>0.715</v>
       </c>
       <c r="M70">
-        <v>0.8580871040000002</v>
+        <v>0.8707060320000002</v>
       </c>
       <c r="N70">
-        <v>-0.1430871040000002</v>
+        <v>-0.1557060320000002</v>
       </c>
       <c r="O70">
-        <v>-0.02146306560000004</v>
+        <v>-0.02335590480000003</v>
       </c>
       <c r="P70">
-        <v>-0.1216240384000002</v>
+        <v>-0.1323501272000002</v>
       </c>
       <c r="Q70">
-        <v>0.1373759615999998</v>
+        <v>0.1266498727999998</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1946629398499362</v>
+        <v>0.1994649701676761</v>
       </c>
       <c r="T70">
-        <v>2.726477021856691</v>
+        <v>2.814427893529488</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.1249873113114633</v>
+        <v>0.1231759010026015</v>
       </c>
       <c r="W70">
-        <v>0.1284518626994772</v>
+        <v>0.1287177777328181</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8332487420764219</v>
+        <v>0.8211726733506767</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1506494073876241</v>
+        <v>0.1516594073876241</v>
       </c>
       <c r="C71">
-        <v>-1.580632413158255</v>
+        <v>-1.706574817813251</v>
       </c>
       <c r="D71">
-        <v>4.190607586841746</v>
+        <v>4.15062518218675</v>
       </c>
       <c r="E71">
-        <v>5.855240000000001</v>
+        <v>5.941200000000001</v>
       </c>
       <c r="F71">
-        <v>5.931240000000001</v>
+        <v>6.017200000000001</v>
       </c>
       <c r="G71">
         <v>0.16</v>
@@ -7109,37 +7109,37 @@
         <v>0.715</v>
       </c>
       <c r="M71">
-        <v>0.8707060320000002</v>
+        <v>0.8833249600000002</v>
       </c>
       <c r="N71">
-        <v>-0.1557060320000002</v>
+        <v>-0.1683249600000002</v>
       </c>
       <c r="O71">
-        <v>-0.02335590480000003</v>
+        <v>-0.02524874400000003</v>
       </c>
       <c r="P71">
-        <v>-0.1323501272000002</v>
+        <v>-0.1430762160000002</v>
       </c>
       <c r="Q71">
-        <v>0.1266498727999998</v>
+        <v>0.1159237839999998</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1994649701676761</v>
+        <v>0.204587135839932</v>
       </c>
       <c r="T71">
-        <v>2.814427893529488</v>
+        <v>2.908242156647137</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.1231759010026015</v>
+        <v>0.1214162452739929</v>
       </c>
       <c r="W71">
-        <v>0.1287177777328181</v>
+        <v>0.1289760951937779</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8211726733506767</v>
+        <v>0.8094416351599527</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1516594073876241</v>
+        <v>0.1921993232945067</v>
       </c>
       <c r="C72">
-        <v>-1.706574817813251</v>
+        <v>-2.941898025649567</v>
       </c>
       <c r="D72">
-        <v>4.15062518218675</v>
+        <v>3.001261974350434</v>
       </c>
       <c r="E72">
-        <v>5.941200000000001</v>
+        <v>6.027160000000001</v>
       </c>
       <c r="F72">
-        <v>6.017200000000001</v>
+        <v>6.103160000000001</v>
       </c>
       <c r="G72">
         <v>0.16</v>
@@ -7191,45 +7191,45 @@
         <v>0.715</v>
       </c>
       <c r="M72">
-        <v>0.8833249600000002</v>
+        <v>1.225514528</v>
       </c>
       <c r="N72">
-        <v>-0.1683249600000002</v>
+        <v>-0.5105145280000002</v>
       </c>
       <c r="O72">
-        <v>-0.02524874400000003</v>
+        <v>-0.07657717920000003</v>
       </c>
       <c r="P72">
-        <v>-0.1430762160000002</v>
+        <v>-0.4339373488000002</v>
       </c>
       <c r="Q72">
-        <v>0.1159237839999998</v>
+        <v>-0.1749373488000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.204587135839932</v>
+        <v>0.2141657126167663</v>
       </c>
       <c r="T72">
-        <v>2.908242156647137</v>
+        <v>3.083677154172077</v>
       </c>
       <c r="U72">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1214162452739929</v>
+        <v>0.08751426241762185</v>
       </c>
       <c r="W72">
-        <v>0.1289760951937779</v>
+        <v>0.1832271361065415</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.8094416351599527</v>
+        <v>0.583428416117479</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1921993232945067</v>
+        <v>0.1937493232945067</v>
       </c>
       <c r="C73">
-        <v>-2.941898025649566</v>
+        <v>-3.059300927561209</v>
       </c>
       <c r="D73">
-        <v>3.001261974350434</v>
+        <v>2.969819072438791</v>
       </c>
       <c r="E73">
-        <v>6.02716</v>
+        <v>6.11312</v>
       </c>
       <c r="F73">
-        <v>6.10316</v>
+        <v>6.18912</v>
       </c>
       <c r="G73">
         <v>0.16</v>
@@ -7273,37 +7273,37 @@
         <v>0.715</v>
       </c>
       <c r="M73">
-        <v>1.225514528</v>
+        <v>1.242775296</v>
       </c>
       <c r="N73">
-        <v>-0.510514528</v>
+        <v>-0.5277752960000001</v>
       </c>
       <c r="O73">
-        <v>-0.0765771792</v>
+        <v>-0.0791662944</v>
       </c>
       <c r="P73">
-        <v>-0.4339373488</v>
+        <v>-0.4486090016000001</v>
       </c>
       <c r="Q73">
-        <v>-0.1749373487999999</v>
+        <v>-0.1896090016</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2141657126167662</v>
+        <v>0.2201787737816508</v>
       </c>
       <c r="T73">
-        <v>3.083677154172076</v>
+        <v>3.193808481106793</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.08751426241762186</v>
+        <v>0.08629878655071044</v>
       </c>
       <c r="W73">
-        <v>0.1832271361065415</v>
+        <v>0.1834712036606173</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5834284161174791</v>
+        <v>0.5753252436714029</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1937493232945067</v>
+        <v>0.1952993232945067</v>
       </c>
       <c r="C74">
-        <v>-3.059300927561209</v>
+        <v>-3.176051833237832</v>
       </c>
       <c r="D74">
-        <v>2.969819072438791</v>
+        <v>2.939028166762168</v>
       </c>
       <c r="E74">
-        <v>6.11312</v>
+        <v>6.19908</v>
       </c>
       <c r="F74">
-        <v>6.18912</v>
+        <v>6.27508</v>
       </c>
       <c r="G74">
         <v>0.16</v>
@@ -7355,37 +7355,37 @@
         <v>0.715</v>
       </c>
       <c r="M74">
-        <v>1.242775296</v>
+        <v>1.260036064</v>
       </c>
       <c r="N74">
-        <v>-0.5277752960000001</v>
+        <v>-0.5450360640000002</v>
       </c>
       <c r="O74">
-        <v>-0.0791662944</v>
+        <v>-0.08175540960000002</v>
       </c>
       <c r="P74">
-        <v>-0.4486090016000001</v>
+        <v>-0.4632806544000001</v>
       </c>
       <c r="Q74">
-        <v>-0.1896090016</v>
+        <v>-0.2042806544000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2201787737816508</v>
+        <v>0.2266372468846748</v>
       </c>
       <c r="T74">
-        <v>3.193808481106793</v>
+        <v>3.312097684110748</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.08629878655071044</v>
+        <v>0.08511661139248153</v>
       </c>
       <c r="W74">
-        <v>0.1834712036606173</v>
+        <v>0.1837085844323897</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5753252436714029</v>
+        <v>0.5674440759498769</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1952993232945067</v>
+        <v>0.1968493232945067</v>
       </c>
       <c r="C75">
-        <v>-3.176051833237832</v>
+        <v>-3.292170814152956</v>
       </c>
       <c r="D75">
-        <v>2.939028166762168</v>
+        <v>2.908869185847044</v>
       </c>
       <c r="E75">
-        <v>6.19908</v>
+        <v>6.28504</v>
       </c>
       <c r="F75">
-        <v>6.27508</v>
+        <v>6.36104</v>
       </c>
       <c r="G75">
         <v>0.16</v>
@@ -7437,37 +7437,37 @@
         <v>0.715</v>
       </c>
       <c r="M75">
-        <v>1.260036064</v>
+        <v>1.277296832</v>
       </c>
       <c r="N75">
-        <v>-0.5450360640000002</v>
+        <v>-0.562296832</v>
       </c>
       <c r="O75">
-        <v>-0.08175540960000002</v>
+        <v>-0.0843445248</v>
       </c>
       <c r="P75">
-        <v>-0.4632806544000001</v>
+        <v>-0.4779523072</v>
       </c>
       <c r="Q75">
-        <v>-0.2042806544000001</v>
+        <v>-0.2189523072</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2266372468846748</v>
+        <v>0.2335925256110085</v>
       </c>
       <c r="T75">
-        <v>3.312097684110748</v>
+        <v>3.439486056576546</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.08511661139248153</v>
+        <v>0.08396638691420476</v>
       </c>
       <c r="W75">
-        <v>0.1837085844323897</v>
+        <v>0.1839395495076277</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5674440759498769</v>
+        <v>0.5597759127613651</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1968493232945067</v>
+        <v>0.1983993232945067</v>
       </c>
       <c r="C76">
-        <v>-3.292170814152956</v>
+        <v>-3.407677126290666</v>
       </c>
       <c r="D76">
-        <v>2.908869185847044</v>
+        <v>2.879322873709333</v>
       </c>
       <c r="E76">
-        <v>6.28504</v>
+        <v>6.371</v>
       </c>
       <c r="F76">
-        <v>6.36104</v>
+        <v>6.447</v>
       </c>
       <c r="G76">
         <v>0.16</v>
@@ -7519,37 +7519,37 @@
         <v>0.715</v>
       </c>
       <c r="M76">
-        <v>1.277296832</v>
+        <v>1.2945576</v>
       </c>
       <c r="N76">
-        <v>-0.562296832</v>
+        <v>-0.5795576000000001</v>
       </c>
       <c r="O76">
-        <v>-0.0843445248</v>
+        <v>-0.08693364000000002</v>
       </c>
       <c r="P76">
-        <v>-0.4779523072</v>
+        <v>-0.4926239600000001</v>
       </c>
       <c r="Q76">
-        <v>-0.2189523072</v>
+        <v>-0.2336239600000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2335925256110085</v>
+        <v>0.2411042266354489</v>
       </c>
       <c r="T76">
-        <v>3.439486056576546</v>
+        <v>3.577065498839608</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.08396638691420476</v>
+        <v>0.08284683508868203</v>
       </c>
       <c r="W76">
-        <v>0.1839395495076277</v>
+        <v>0.1841643555141926</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5597759127613651</v>
+        <v>0.5523122339245468</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1983993232945067</v>
+        <v>0.1999493232945067</v>
       </c>
       <c r="C77">
-        <v>-3.407677126290666</v>
+        <v>-3.522589251145104</v>
       </c>
       <c r="D77">
-        <v>2.879322873709333</v>
+        <v>2.850370748854896</v>
       </c>
       <c r="E77">
-        <v>6.371</v>
+        <v>6.45696</v>
       </c>
       <c r="F77">
-        <v>6.447</v>
+        <v>6.53296</v>
       </c>
       <c r="G77">
         <v>0.16</v>
@@ -7601,37 +7601,37 @@
         <v>0.715</v>
       </c>
       <c r="M77">
-        <v>1.2945576</v>
+        <v>1.311818368</v>
       </c>
       <c r="N77">
-        <v>-0.5795576000000001</v>
+        <v>-0.596818368</v>
       </c>
       <c r="O77">
-        <v>-0.08693364000000002</v>
+        <v>-0.0895227552</v>
       </c>
       <c r="P77">
-        <v>-0.4926239600000001</v>
+        <v>-0.5072956128</v>
       </c>
       <c r="Q77">
-        <v>-0.2336239600000001</v>
+        <v>-0.2482956128</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2411042266354489</v>
+        <v>0.2492419027452592</v>
       </c>
       <c r="T77">
-        <v>3.577065498839608</v>
+        <v>3.726109894624592</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.08284683508868203</v>
+        <v>0.08175674515330464</v>
       </c>
       <c r="W77">
-        <v>0.1841643555141926</v>
+        <v>0.1843832455732164</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5523122339245468</v>
+        <v>0.5450449676886976</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1999493232945067</v>
+        <v>0.2014993232945067</v>
       </c>
       <c r="C78">
-        <v>-3.522589251145104</v>
+        <v>-3.636924934271023</v>
       </c>
       <c r="D78">
-        <v>2.850370748854896</v>
+        <v>2.821995065728977</v>
       </c>
       <c r="E78">
-        <v>6.45696</v>
+        <v>6.542920000000001</v>
       </c>
       <c r="F78">
-        <v>6.53296</v>
+        <v>6.61892</v>
       </c>
       <c r="G78">
         <v>0.16</v>
@@ -7683,37 +7683,37 @@
         <v>0.715</v>
       </c>
       <c r="M78">
-        <v>1.311818368</v>
+        <v>1.329079136</v>
       </c>
       <c r="N78">
-        <v>-0.596818368</v>
+        <v>-0.6140791360000001</v>
       </c>
       <c r="O78">
-        <v>-0.0895227552</v>
+        <v>-0.0921118704</v>
       </c>
       <c r="P78">
-        <v>-0.5072956128</v>
+        <v>-0.5219672656000001</v>
       </c>
       <c r="Q78">
-        <v>-0.2482956128</v>
+        <v>-0.2629672656000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2492419027452592</v>
+        <v>0.2580872028646183</v>
       </c>
       <c r="T78">
-        <v>3.726109894624592</v>
+        <v>3.888114672651749</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.08175674515330464</v>
+        <v>0.08069496924222275</v>
       </c>
       <c r="W78">
-        <v>0.1843832455732164</v>
+        <v>0.1845964501761617</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5450449676886976</v>
+        <v>0.5379664616148183</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2014993232945067</v>
+        <v>0.2030493232945067</v>
       </c>
       <c r="C79">
-        <v>-3.636924934271023</v>
+        <v>-3.75070122155442</v>
       </c>
       <c r="D79">
-        <v>2.821995065728977</v>
+        <v>2.79417877844558</v>
       </c>
       <c r="E79">
-        <v>6.542920000000001</v>
+        <v>6.628880000000001</v>
       </c>
       <c r="F79">
-        <v>6.61892</v>
+        <v>6.70488</v>
       </c>
       <c r="G79">
         <v>0.16</v>
@@ -7765,37 +7765,37 @@
         <v>0.715</v>
       </c>
       <c r="M79">
-        <v>1.329079136</v>
+        <v>1.346339904</v>
       </c>
       <c r="N79">
-        <v>-0.6140791360000001</v>
+        <v>-0.6313399040000002</v>
       </c>
       <c r="O79">
-        <v>-0.0921118704</v>
+        <v>-0.09470098560000002</v>
       </c>
       <c r="P79">
-        <v>-0.5219672656000001</v>
+        <v>-0.5366389184000001</v>
       </c>
       <c r="Q79">
-        <v>-0.2629672656000001</v>
+        <v>-0.2776389184000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2580872028646183</v>
+        <v>0.2677366211766464</v>
       </c>
       <c r="T79">
-        <v>3.888114672651749</v>
+        <v>4.064847157772282</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.08069496924222275</v>
+        <v>0.07966041835450194</v>
       </c>
       <c r="W79">
-        <v>0.1845964501761617</v>
+        <v>0.184804187994416</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5379664616148183</v>
+        <v>0.5310694556966796</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2030493232945067</v>
+        <v>0.2045993232945067</v>
       </c>
       <c r="C80">
-        <v>-3.75070122155442</v>
+        <v>-3.863934493358977</v>
       </c>
       <c r="D80">
-        <v>2.79417877844558</v>
+        <v>2.766905506641023</v>
       </c>
       <c r="E80">
-        <v>6.628880000000001</v>
+        <v>6.714840000000001</v>
       </c>
       <c r="F80">
-        <v>6.70488</v>
+        <v>6.79084</v>
       </c>
       <c r="G80">
         <v>0.16</v>
@@ -7847,37 +7847,37 @@
         <v>0.715</v>
       </c>
       <c r="M80">
-        <v>1.346339904</v>
+        <v>1.363600672</v>
       </c>
       <c r="N80">
-        <v>-0.6313399040000002</v>
+        <v>-0.648600672</v>
       </c>
       <c r="O80">
-        <v>-0.09470098560000002</v>
+        <v>-0.0972901008</v>
       </c>
       <c r="P80">
-        <v>-0.5366389184000001</v>
+        <v>-0.5513105712</v>
       </c>
       <c r="Q80">
-        <v>-0.2776389184000001</v>
+        <v>-0.2923105712</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2677366211766464</v>
+        <v>0.2783050317088677</v>
       </c>
       <c r="T80">
-        <v>4.064847157772282</v>
+        <v>4.258411308142391</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.07966041835450194</v>
+        <v>0.0786520586284956</v>
       </c>
       <c r="W80">
-        <v>0.184804187994416</v>
+        <v>0.1850066666273981</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5310694556966796</v>
+        <v>0.524347057523304</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2045993232945067</v>
+        <v>0.2061493232945067</v>
       </c>
       <c r="C81">
-        <v>-3.863934493358977</v>
+        <v>-3.976640496692067</v>
       </c>
       <c r="D81">
-        <v>2.766905506641023</v>
+        <v>2.740159503307933</v>
       </c>
       <c r="E81">
-        <v>6.714840000000001</v>
+        <v>6.800800000000001</v>
       </c>
       <c r="F81">
-        <v>6.79084</v>
+        <v>6.8768</v>
       </c>
       <c r="G81">
         <v>0.16</v>
@@ -7929,37 +7929,37 @@
         <v>0.715</v>
       </c>
       <c r="M81">
-        <v>1.363600672</v>
+        <v>1.38086144</v>
       </c>
       <c r="N81">
-        <v>-0.648600672</v>
+        <v>-0.6658614400000001</v>
       </c>
       <c r="O81">
-        <v>-0.0972901008</v>
+        <v>-0.09987921600000002</v>
       </c>
       <c r="P81">
-        <v>-0.5513105712</v>
+        <v>-0.5659822240000001</v>
       </c>
       <c r="Q81">
-        <v>-0.2923105712</v>
+        <v>-0.3069822240000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2783050317088677</v>
+        <v>0.2899302832943111</v>
       </c>
       <c r="T81">
-        <v>4.258411308142391</v>
+        <v>4.471331873549511</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.0786520586284956</v>
+        <v>0.07766890789563939</v>
       </c>
       <c r="W81">
-        <v>0.1850066666273981</v>
+        <v>0.1852040832945556</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.524347057523304</v>
+        <v>0.5177927193042626</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2061493232945067</v>
+        <v>0.2076993232945067</v>
       </c>
       <c r="C82">
-        <v>-3.976640496692067</v>
+        <v>-4.088834375523057</v>
       </c>
       <c r="D82">
-        <v>2.740159503307933</v>
+        <v>2.713925624476943</v>
       </c>
       <c r="E82">
-        <v>6.800800000000001</v>
+        <v>6.886760000000001</v>
       </c>
       <c r="F82">
-        <v>6.8768</v>
+        <v>6.96276</v>
       </c>
       <c r="G82">
         <v>0.16</v>
@@ -8011,37 +8011,37 @@
         <v>0.715</v>
       </c>
       <c r="M82">
-        <v>1.38086144</v>
+        <v>1.398122208</v>
       </c>
       <c r="N82">
-        <v>-0.6658614400000001</v>
+        <v>-0.6831222080000002</v>
       </c>
       <c r="O82">
-        <v>-0.09987921600000002</v>
+        <v>-0.1024683312</v>
       </c>
       <c r="P82">
-        <v>-0.5659822240000001</v>
+        <v>-0.5806538768000002</v>
       </c>
       <c r="Q82">
-        <v>-0.3069822240000001</v>
+        <v>-0.3216538768000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2899302832943111</v>
+        <v>0.3027792455729591</v>
       </c>
       <c r="T82">
-        <v>4.471331873549511</v>
+        <v>4.706665130052118</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.07766890789563939</v>
+        <v>0.07671003248952038</v>
       </c>
       <c r="W82">
-        <v>0.1852040832945556</v>
+        <v>0.1853966254761043</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5177927193042626</v>
+        <v>0.5114002165968026</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2076993232945067</v>
+        <v>0.2092493232945067</v>
       </c>
       <c r="C83">
-        <v>-4.088834375523057</v>
+        <v>-4.200530699376536</v>
       </c>
       <c r="D83">
-        <v>2.713925624476943</v>
+        <v>2.688189300623464</v>
       </c>
       <c r="E83">
-        <v>6.886760000000001</v>
+        <v>6.972720000000001</v>
       </c>
       <c r="F83">
-        <v>6.96276</v>
+        <v>7.04872</v>
       </c>
       <c r="G83">
         <v>0.16</v>
@@ -8093,37 +8093,37 @@
         <v>0.715</v>
       </c>
       <c r="M83">
-        <v>1.398122208</v>
+        <v>1.415382976</v>
       </c>
       <c r="N83">
-        <v>-0.6831222080000002</v>
+        <v>-0.7003829760000001</v>
       </c>
       <c r="O83">
-        <v>-0.1024683312</v>
+        <v>-0.1050574464</v>
       </c>
       <c r="P83">
-        <v>-0.5806538768000002</v>
+        <v>-0.5953255296000001</v>
       </c>
       <c r="Q83">
-        <v>-0.3216538768000002</v>
+        <v>-0.3363255296000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3027792455729591</v>
+        <v>0.3170558703270124</v>
       </c>
       <c r="T83">
-        <v>4.706665130052118</v>
+        <v>4.968146526166124</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.07671003248952038</v>
+        <v>0.07577454428842868</v>
       </c>
       <c r="W83">
-        <v>0.1853966254761043</v>
+        <v>0.1855844715068835</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5114002165968026</v>
+        <v>0.5051636285895246</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2092493232945067</v>
+        <v>0.2403294687355241</v>
       </c>
       <c r="C84">
-        <v>-4.200530699376536</v>
+        <v>-4.71598508384923</v>
       </c>
       <c r="D84">
-        <v>2.688189300623464</v>
+        <v>2.258694916150771</v>
       </c>
       <c r="E84">
-        <v>6.972720000000001</v>
+        <v>7.058680000000001</v>
       </c>
       <c r="F84">
-        <v>7.04872</v>
+        <v>7.13468</v>
       </c>
       <c r="G84">
         <v>0.16</v>
@@ -8175,45 +8175,45 @@
         <v>0.715</v>
       </c>
       <c r="M84">
-        <v>1.415382976</v>
+        <v>1.682357544</v>
       </c>
       <c r="N84">
-        <v>-0.7003829760000001</v>
+        <v>-0.9673575440000003</v>
       </c>
       <c r="O84">
-        <v>-0.1050574464</v>
+        <v>-0.1451036316</v>
       </c>
       <c r="P84">
-        <v>-0.5953255296000001</v>
+        <v>-0.8222539124000002</v>
       </c>
       <c r="Q84">
-        <v>-0.3363255296000001</v>
+        <v>-0.5632539124000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3170558703270124</v>
+        <v>0.3358364829404685</v>
       </c>
       <c r="T84">
-        <v>4.968146526166124</v>
+        <v>5.312120041660297</v>
       </c>
       <c r="U84">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07577454428842868</v>
+        <v>0.06374982558404362</v>
       </c>
       <c r="W84">
-        <v>0.1855844715068835</v>
+        <v>0.2207677911272825</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.5051636285895246</v>
+        <v>0.4249988372269574</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2403294687355241</v>
+        <v>0.2422294687355241</v>
       </c>
       <c r="C85">
-        <v>-4.71598508384923</v>
+        <v>-4.823792723963068</v>
       </c>
       <c r="D85">
-        <v>2.258694916150771</v>
+        <v>2.236847276036932</v>
       </c>
       <c r="E85">
-        <v>7.058680000000001</v>
+        <v>7.144640000000001</v>
       </c>
       <c r="F85">
-        <v>7.13468</v>
+        <v>7.22064</v>
       </c>
       <c r="G85">
         <v>0.16</v>
@@ -8257,37 +8257,37 @@
         <v>0.715</v>
       </c>
       <c r="M85">
-        <v>1.682357544</v>
+        <v>1.702626912</v>
       </c>
       <c r="N85">
-        <v>-0.9673575440000003</v>
+        <v>-0.9876269120000002</v>
       </c>
       <c r="O85">
-        <v>-0.1451036316</v>
+        <v>-0.1481440368</v>
       </c>
       <c r="P85">
-        <v>-0.8222539124000002</v>
+        <v>-0.8394828752000002</v>
       </c>
       <c r="Q85">
-        <v>-0.5632539124000002</v>
+        <v>-0.5804828752000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3358364829404685</v>
+        <v>0.3539637631242478</v>
       </c>
       <c r="T85">
-        <v>5.312120041660297</v>
+        <v>5.644127544264066</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06374982558404362</v>
+        <v>0.06299089908899548</v>
       </c>
       <c r="W85">
-        <v>0.2207677911272825</v>
+        <v>0.2209467459948149</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4249988372269574</v>
+        <v>0.4199393272599699</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2422294687355241</v>
+        <v>0.2441294687355241</v>
       </c>
       <c r="C86">
-        <v>-4.823792723963068</v>
+        <v>-4.931181762479467</v>
       </c>
       <c r="D86">
-        <v>2.236847276036931</v>
+        <v>2.215418237520533</v>
       </c>
       <c r="E86">
-        <v>7.14464</v>
+        <v>7.2306</v>
       </c>
       <c r="F86">
-        <v>7.22064</v>
+        <v>7.3066</v>
       </c>
       <c r="G86">
         <v>0.16</v>
@@ -8339,37 +8339,37 @@
         <v>0.715</v>
       </c>
       <c r="M86">
-        <v>1.702626912</v>
+        <v>1.72289628</v>
       </c>
       <c r="N86">
-        <v>-0.987626912</v>
+        <v>-1.00789628</v>
       </c>
       <c r="O86">
-        <v>-0.1481440368</v>
+        <v>-0.151184442</v>
       </c>
       <c r="P86">
-        <v>-0.8394828752</v>
+        <v>-0.8567118380000002</v>
       </c>
       <c r="Q86">
-        <v>-0.5804828752</v>
+        <v>-0.5977118380000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3539637631242477</v>
+        <v>0.3745080139991975</v>
       </c>
       <c r="T86">
-        <v>5.644127544264062</v>
+        <v>6.020402713881667</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06299089908899548</v>
+        <v>0.06224982968794848</v>
       </c>
       <c r="W86">
-        <v>0.2209467459948149</v>
+        <v>0.2211214901595818</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.41993932725997</v>
+        <v>0.4149988645863231</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2441294687355241</v>
+        <v>0.2460294687355241</v>
       </c>
       <c r="C87">
-        <v>-4.931181762479467</v>
+        <v>-5.038164115871657</v>
       </c>
       <c r="D87">
-        <v>2.215418237520533</v>
+        <v>2.194395884128342</v>
       </c>
       <c r="E87">
-        <v>7.2306</v>
+        <v>7.31656</v>
       </c>
       <c r="F87">
-        <v>7.3066</v>
+        <v>7.39256</v>
       </c>
       <c r="G87">
         <v>0.16</v>
@@ -8421,37 +8421,37 @@
         <v>0.715</v>
       </c>
       <c r="M87">
-        <v>1.72289628</v>
+        <v>1.743165648</v>
       </c>
       <c r="N87">
-        <v>-1.00789628</v>
+        <v>-1.028165648</v>
       </c>
       <c r="O87">
-        <v>-0.151184442</v>
+        <v>-0.1542248472</v>
       </c>
       <c r="P87">
-        <v>-0.8567118380000002</v>
+        <v>-0.8739408007999999</v>
       </c>
       <c r="Q87">
-        <v>-0.5977118380000002</v>
+        <v>-0.6149408007999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3745080139991975</v>
+        <v>0.397987157856283</v>
       </c>
       <c r="T87">
-        <v>6.020402713881667</v>
+        <v>6.450431479158929</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06224982968794848</v>
+        <v>0.06152599445901885</v>
       </c>
       <c r="W87">
-        <v>0.2211214901595818</v>
+        <v>0.2212921705065634</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4149988645863231</v>
+        <v>0.410173296393459</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2460294687355241</v>
+        <v>0.2479294687355241</v>
       </c>
       <c r="C88">
-        <v>-5.038164115871657</v>
+        <v>-5.144751252557498</v>
       </c>
       <c r="D88">
-        <v>2.194395884128342</v>
+        <v>2.173768747442502</v>
       </c>
       <c r="E88">
-        <v>7.31656</v>
+        <v>7.40252</v>
       </c>
       <c r="F88">
-        <v>7.39256</v>
+        <v>7.47852</v>
       </c>
       <c r="G88">
         <v>0.16</v>
@@ -8503,37 +8503,37 @@
         <v>0.715</v>
       </c>
       <c r="M88">
-        <v>1.743165648</v>
+        <v>1.763435016</v>
       </c>
       <c r="N88">
-        <v>-1.028165648</v>
+        <v>-1.048435016</v>
       </c>
       <c r="O88">
-        <v>-0.1542248472</v>
+        <v>-0.1572652524</v>
       </c>
       <c r="P88">
-        <v>-0.8739408007999999</v>
+        <v>-0.8911697636</v>
       </c>
       <c r="Q88">
-        <v>-0.6149408007999999</v>
+        <v>-0.6321697636</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.397987157856283</v>
+        <v>0.4250784776913817</v>
       </c>
       <c r="T88">
-        <v>6.450431479158929</v>
+        <v>6.946618516017307</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06152599445901885</v>
+        <v>0.06081879912040943</v>
       </c>
       <c r="W88">
-        <v>0.2212921705065634</v>
+        <v>0.2214589271674075</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.410173296393459</v>
+        <v>0.4054586608027296</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2479294687355241</v>
+        <v>0.2498294687355241</v>
       </c>
       <c r="C89">
-        <v>-5.144751252557498</v>
+        <v>-5.250954213761766</v>
       </c>
       <c r="D89">
-        <v>2.173768747442502</v>
+        <v>2.153525786238234</v>
       </c>
       <c r="E89">
-        <v>7.40252</v>
+        <v>7.488480000000001</v>
       </c>
       <c r="F89">
-        <v>7.47852</v>
+        <v>7.564480000000001</v>
       </c>
       <c r="G89">
         <v>0.16</v>
@@ -8585,37 +8585,37 @@
         <v>0.715</v>
       </c>
       <c r="M89">
-        <v>1.763435016</v>
+        <v>1.783704384</v>
       </c>
       <c r="N89">
-        <v>-1.048435016</v>
+        <v>-1.068704384</v>
       </c>
       <c r="O89">
-        <v>-0.1572652524</v>
+        <v>-0.1603056576</v>
       </c>
       <c r="P89">
-        <v>-0.8911697636</v>
+        <v>-0.9083987264000001</v>
       </c>
       <c r="Q89">
-        <v>-0.6321697636</v>
+        <v>-0.6493987264000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4250784776913817</v>
+        <v>0.4566850174989969</v>
       </c>
       <c r="T89">
-        <v>6.946618516017307</v>
+        <v>7.525503392352085</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06081879912040943</v>
+        <v>0.06012767640313205</v>
       </c>
       <c r="W89">
-        <v>0.2214589271674075</v>
+        <v>0.2216218939041415</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4054586608027296</v>
+        <v>0.4008511760208804</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2498294687355241</v>
+        <v>0.2517294687355242</v>
       </c>
       <c r="C90">
-        <v>-5.250954213761766</v>
+        <v>-5.356783633223571</v>
       </c>
       <c r="D90">
-        <v>2.153525786238234</v>
+        <v>2.13365636677643</v>
       </c>
       <c r="E90">
-        <v>7.488480000000001</v>
+        <v>7.574440000000001</v>
       </c>
       <c r="F90">
-        <v>7.564480000000001</v>
+        <v>7.650440000000001</v>
       </c>
       <c r="G90">
         <v>0.16</v>
@@ -8667,37 +8667,37 @@
         <v>0.715</v>
       </c>
       <c r="M90">
-        <v>1.783704384</v>
+        <v>1.803973752</v>
       </c>
       <c r="N90">
-        <v>-1.068704384</v>
+        <v>-1.088973752</v>
       </c>
       <c r="O90">
-        <v>-0.1603056576</v>
+        <v>-0.1633460628</v>
       </c>
       <c r="P90">
-        <v>-0.9083987264000001</v>
+        <v>-0.9256276892000002</v>
       </c>
       <c r="Q90">
-        <v>-0.6493987264000001</v>
+        <v>-0.6666276892000002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4566850174989969</v>
+        <v>0.4940382009079967</v>
       </c>
       <c r="T90">
-        <v>7.525503392352085</v>
+        <v>8.209640064384093</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06012767640313205</v>
+        <v>0.05945208453343392</v>
       </c>
       <c r="W90">
-        <v>0.2216218939041415</v>
+        <v>0.2217811984670163</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4008511760208804</v>
+        <v>0.396347230222893</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2517294687355242</v>
+        <v>0.2536294687355241</v>
       </c>
       <c r="C91">
-        <v>-5.356783633223571</v>
+        <v>-5.462249755822739</v>
       </c>
       <c r="D91">
-        <v>2.13365636677643</v>
+        <v>2.114150244177261</v>
       </c>
       <c r="E91">
-        <v>7.574440000000001</v>
+        <v>7.660400000000001</v>
       </c>
       <c r="F91">
-        <v>7.650440000000001</v>
+        <v>7.736400000000001</v>
       </c>
       <c r="G91">
         <v>0.16</v>
@@ -8749,37 +8749,37 @@
         <v>0.715</v>
       </c>
       <c r="M91">
-        <v>1.803973752</v>
+        <v>1.82424312</v>
       </c>
       <c r="N91">
-        <v>-1.088973752</v>
+        <v>-1.10924312</v>
       </c>
       <c r="O91">
-        <v>-0.1633460628</v>
+        <v>-0.166386468</v>
       </c>
       <c r="P91">
-        <v>-0.9256276892000002</v>
+        <v>-0.9428566520000004</v>
       </c>
       <c r="Q91">
-        <v>-0.6666276892000002</v>
+        <v>-0.6838566520000003</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4940382009079967</v>
+        <v>0.5388620209987963</v>
       </c>
       <c r="T91">
-        <v>8.209640064384093</v>
+        <v>9.030604070822502</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05945208453343392</v>
+        <v>0.05879150581639578</v>
       </c>
       <c r="W91">
-        <v>0.2217811984670163</v>
+        <v>0.2219369629284939</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.396347230222893</v>
+        <v>0.3919433721093051</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2536294687355241</v>
+        <v>0.2555294687355241</v>
       </c>
       <c r="C92">
-        <v>-5.462249755822739</v>
+        <v>-5.567362455193766</v>
       </c>
       <c r="D92">
-        <v>2.114150244177261</v>
+        <v>2.094997544806234</v>
       </c>
       <c r="E92">
-        <v>7.660400000000001</v>
+        <v>7.746360000000001</v>
       </c>
       <c r="F92">
-        <v>7.736400000000001</v>
+        <v>7.822360000000001</v>
       </c>
       <c r="G92">
         <v>0.16</v>
@@ -8831,37 +8831,37 @@
         <v>0.715</v>
       </c>
       <c r="M92">
-        <v>1.82424312</v>
+        <v>1.844512488</v>
       </c>
       <c r="N92">
-        <v>-1.10924312</v>
+        <v>-1.129512488</v>
       </c>
       <c r="O92">
-        <v>-0.166386468</v>
+        <v>-0.1694268732</v>
       </c>
       <c r="P92">
-        <v>-0.9428566520000004</v>
+        <v>-0.9600856148000001</v>
       </c>
       <c r="Q92">
-        <v>-0.6838566520000003</v>
+        <v>-0.7010856148000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5388620209987963</v>
+        <v>0.5936466899986627</v>
       </c>
       <c r="T92">
-        <v>9.030604070822502</v>
+        <v>10.03400452313612</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05879150581639578</v>
+        <v>0.0581454453129189</v>
       </c>
       <c r="W92">
-        <v>0.2219369629284939</v>
+        <v>0.2220893039952137</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3919433721093051</v>
+        <v>0.3876363020861261</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2555294687355241</v>
+        <v>0.2574294687355241</v>
       </c>
       <c r="C93">
-        <v>-5.567362455193766</v>
+        <v>-5.672131250390934</v>
       </c>
       <c r="D93">
-        <v>2.094997544806234</v>
+        <v>2.076188749609067</v>
       </c>
       <c r="E93">
-        <v>7.746360000000001</v>
+        <v>7.832320000000001</v>
       </c>
       <c r="F93">
-        <v>7.822360000000001</v>
+        <v>7.908320000000001</v>
       </c>
       <c r="G93">
         <v>0.16</v>
@@ -8913,37 +8913,37 @@
         <v>0.715</v>
       </c>
       <c r="M93">
-        <v>1.844512488</v>
+        <v>1.864781856</v>
       </c>
       <c r="N93">
-        <v>-1.129512488</v>
+        <v>-1.149781856</v>
       </c>
       <c r="O93">
-        <v>-0.1694268732</v>
+        <v>-0.1724672784</v>
       </c>
       <c r="P93">
-        <v>-0.9600856148000001</v>
+        <v>-0.9773145776000002</v>
       </c>
       <c r="Q93">
-        <v>-0.7010856148000001</v>
+        <v>-0.7183145776000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5936466899986627</v>
+        <v>0.6621275262484956</v>
       </c>
       <c r="T93">
-        <v>10.03400452313612</v>
+        <v>11.28825508852813</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0581454453129189</v>
+        <v>0.05751342960299587</v>
       </c>
       <c r="W93">
-        <v>0.2220893039952137</v>
+        <v>0.2222383332996136</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3876363020861261</v>
+        <v>0.3834228640199725</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2574294687355241</v>
+        <v>0.2593294687355241</v>
       </c>
       <c r="C94">
-        <v>-5.672131250390934</v>
+        <v>-5.776565321663706</v>
       </c>
       <c r="D94">
-        <v>2.076188749609067</v>
+        <v>2.057714678336295</v>
       </c>
       <c r="E94">
-        <v>7.832320000000001</v>
+        <v>7.918280000000001</v>
       </c>
       <c r="F94">
-        <v>7.908320000000001</v>
+        <v>7.994280000000001</v>
       </c>
       <c r="G94">
         <v>0.16</v>
@@ -8995,37 +8995,37 @@
         <v>0.715</v>
       </c>
       <c r="M94">
-        <v>1.864781856</v>
+        <v>1.885051224</v>
       </c>
       <c r="N94">
-        <v>-1.149781856</v>
+        <v>-1.170051224</v>
       </c>
       <c r="O94">
-        <v>-0.1724672784</v>
+        <v>-0.1755076836</v>
       </c>
       <c r="P94">
-        <v>-0.9773145776000002</v>
+        <v>-0.9945435404000003</v>
       </c>
       <c r="Q94">
-        <v>-0.7183145776000002</v>
+        <v>-0.7355435404000003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6621275262484956</v>
+        <v>0.7501743157125664</v>
       </c>
       <c r="T94">
-        <v>11.28825508852813</v>
+        <v>12.90086295831787</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05751342960299587</v>
+        <v>0.05689500562877011</v>
       </c>
       <c r="W94">
-        <v>0.2222383332996136</v>
+        <v>0.222384157672736</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3834228640199725</v>
+        <v>0.379300037525134</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2593294687355241</v>
+        <v>0.2612294687355241</v>
       </c>
       <c r="C95">
-        <v>-5.776565321663706</v>
+        <v>-5.880673525397331</v>
       </c>
       <c r="D95">
-        <v>2.057714678336295</v>
+        <v>2.039566474602669</v>
       </c>
       <c r="E95">
-        <v>7.918280000000001</v>
+        <v>8.004239999999999</v>
       </c>
       <c r="F95">
-        <v>7.994280000000001</v>
+        <v>8.08024</v>
       </c>
       <c r="G95">
         <v>0.16</v>
@@ -9077,37 +9077,37 @@
         <v>0.715</v>
       </c>
       <c r="M95">
-        <v>1.885051224</v>
+        <v>1.905320592</v>
       </c>
       <c r="N95">
-        <v>-1.170051224</v>
+        <v>-1.190320592</v>
       </c>
       <c r="O95">
-        <v>-0.1755076836</v>
+        <v>-0.1785480888</v>
       </c>
       <c r="P95">
-        <v>-0.9945435404000003</v>
+        <v>-1.0117725032</v>
       </c>
       <c r="Q95">
-        <v>-0.7355435404000003</v>
+        <v>-0.7527725032</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7501743157125664</v>
+        <v>0.8675700349979943</v>
       </c>
       <c r="T95">
-        <v>12.90086295831787</v>
+        <v>15.05100678470418</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05689500562877011</v>
+        <v>0.05628973961144277</v>
       </c>
       <c r="W95">
-        <v>0.222384157672736</v>
+        <v>0.2225268793996218</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.379300037525134</v>
+        <v>0.3752649307429519</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2612294687355241</v>
+        <v>0.2631294687355241</v>
       </c>
       <c r="C96">
-        <v>-5.880673525397331</v>
+        <v>-5.984464408269735</v>
       </c>
       <c r="D96">
-        <v>2.039566474602669</v>
+        <v>2.021735591730264</v>
       </c>
       <c r="E96">
-        <v>8.004239999999999</v>
+        <v>8.090199999999999</v>
       </c>
       <c r="F96">
-        <v>8.08024</v>
+        <v>8.1662</v>
       </c>
       <c r="G96">
         <v>0.16</v>
@@ -9159,37 +9159,37 @@
         <v>0.715</v>
       </c>
       <c r="M96">
-        <v>1.905320592</v>
+        <v>1.92558996</v>
       </c>
       <c r="N96">
-        <v>-1.190320592</v>
+        <v>-1.21058996</v>
       </c>
       <c r="O96">
-        <v>-0.1785480888</v>
+        <v>-0.181588494</v>
       </c>
       <c r="P96">
-        <v>-1.0117725032</v>
+        <v>-1.029001466</v>
       </c>
       <c r="Q96">
-        <v>-0.7527725032</v>
+        <v>-0.770001466</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8675700349979943</v>
+        <v>1.031924041997594</v>
       </c>
       <c r="T96">
-        <v>15.05100678470418</v>
+        <v>18.06120814164503</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05628973961144277</v>
+        <v>0.05569721603658548</v>
       </c>
       <c r="W96">
-        <v>0.2225268793996218</v>
+        <v>0.2226665964585731</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3752649307429519</v>
+        <v>0.3713147735772365</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2631294687355241</v>
+        <v>0.2650294687355241</v>
       </c>
       <c r="C97">
-        <v>-5.984464408269735</v>
+        <v>-6.087946220672254</v>
       </c>
       <c r="D97">
-        <v>2.021735591730264</v>
+        <v>2.004213779327746</v>
       </c>
       <c r="E97">
-        <v>8.090199999999999</v>
+        <v>8.176159999999999</v>
       </c>
       <c r="F97">
-        <v>8.1662</v>
+        <v>8.25216</v>
       </c>
       <c r="G97">
         <v>0.16</v>
@@ -9241,37 +9241,37 @@
         <v>0.715</v>
       </c>
       <c r="M97">
-        <v>1.92558996</v>
+        <v>1.945859328</v>
       </c>
       <c r="N97">
-        <v>-1.21058996</v>
+        <v>-1.230859328</v>
       </c>
       <c r="O97">
-        <v>-0.181588494</v>
+        <v>-0.1846288992</v>
       </c>
       <c r="P97">
-        <v>-1.029001466</v>
+        <v>-1.0462304288</v>
       </c>
       <c r="Q97">
-        <v>-0.770001466</v>
+        <v>-0.7872304288000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.031924041997594</v>
+        <v>1.278455052496993</v>
       </c>
       <c r="T97">
-        <v>18.06120814164503</v>
+        <v>22.57651017705629</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05569721603658548</v>
+        <v>0.05511703670287105</v>
       </c>
       <c r="W97">
-        <v>0.2226665964585731</v>
+        <v>0.222803402745463</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3713147735772365</v>
+        <v>0.3674469113524736</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2650294687355241</v>
+        <v>0.2669294687355241</v>
       </c>
       <c r="C98">
-        <v>-6.087946220672254</v>
+        <v>-6.191126929438472</v>
       </c>
       <c r="D98">
-        <v>2.004213779327746</v>
+        <v>1.986993070561529</v>
       </c>
       <c r="E98">
-        <v>8.176159999999999</v>
+        <v>8.262119999999999</v>
       </c>
       <c r="F98">
-        <v>8.25216</v>
+        <v>8.33812</v>
       </c>
       <c r="G98">
         <v>0.16</v>
@@ -9323,37 +9323,37 @@
         <v>0.715</v>
       </c>
       <c r="M98">
-        <v>1.945859328</v>
+        <v>1.966128696</v>
       </c>
       <c r="N98">
-        <v>-1.230859328</v>
+        <v>-1.251128696</v>
       </c>
       <c r="O98">
-        <v>-0.1846288992</v>
+        <v>-0.1876693044</v>
       </c>
       <c r="P98">
-        <v>-1.0462304288</v>
+        <v>-1.0634593916</v>
       </c>
       <c r="Q98">
-        <v>-0.7872304288000002</v>
+        <v>-0.8044593916000004</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.27845505249699</v>
+        <v>1.689340069995986</v>
       </c>
       <c r="T98">
-        <v>22.57651017705623</v>
+        <v>30.10201356940831</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05511703670287105</v>
+        <v>0.05454881982964557</v>
       </c>
       <c r="W98">
-        <v>0.222803402745463</v>
+        <v>0.2229373882841696</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3674469113524736</v>
+        <v>0.3636587988643037</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2669294687355241</v>
+        <v>0.2688294687355241</v>
       </c>
       <c r="C99">
-        <v>-6.191126929438472</v>
+        <v>-6.294014229922443</v>
       </c>
       <c r="D99">
-        <v>1.986993070561529</v>
+        <v>1.970065770077557</v>
       </c>
       <c r="E99">
-        <v>8.262119999999999</v>
+        <v>8.34808</v>
       </c>
       <c r="F99">
-        <v>8.33812</v>
+        <v>8.42408</v>
       </c>
       <c r="G99">
         <v>0.16</v>
@@ -9405,37 +9405,37 @@
         <v>0.715</v>
       </c>
       <c r="M99">
-        <v>1.966128696</v>
+        <v>1.986398064</v>
       </c>
       <c r="N99">
-        <v>-1.251128696</v>
+        <v>-1.271398064</v>
       </c>
       <c r="O99">
-        <v>-0.1876693044</v>
+        <v>-0.1907097096</v>
       </c>
       <c r="P99">
-        <v>-1.0634593916</v>
+        <v>-1.0806883544</v>
       </c>
       <c r="Q99">
-        <v>-0.8044593916000004</v>
+        <v>-0.8216883543999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.689340069995986</v>
+        <v>2.511110104993979</v>
       </c>
       <c r="T99">
-        <v>30.10201356940831</v>
+        <v>45.15302035411246</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05454881982964557</v>
+        <v>0.05399219921913898</v>
       </c>
       <c r="W99">
-        <v>0.2229373882841696</v>
+        <v>0.223068639424127</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3636587988643037</v>
+        <v>0.35994799479426</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2688294687355241</v>
+        <v>0.2707294687355241</v>
       </c>
       <c r="C100">
-        <v>-6.294014229922443</v>
+        <v>-6.39661555746476</v>
       </c>
       <c r="D100">
-        <v>1.970065770077557</v>
+        <v>1.95342444253524</v>
       </c>
       <c r="E100">
-        <v>8.34808</v>
+        <v>8.43404</v>
       </c>
       <c r="F100">
-        <v>8.42408</v>
+        <v>8.51004</v>
       </c>
       <c r="G100">
         <v>0.16</v>
@@ -9487,37 +9487,37 @@
         <v>0.715</v>
       </c>
       <c r="M100">
-        <v>1.986398064</v>
+        <v>2.006667432</v>
       </c>
       <c r="N100">
-        <v>-1.271398064</v>
+        <v>-1.291667432</v>
       </c>
       <c r="O100">
-        <v>-0.1907097096</v>
+        <v>-0.1937501148</v>
       </c>
       <c r="P100">
-        <v>-1.0806883544</v>
+        <v>-1.0979173172</v>
       </c>
       <c r="Q100">
-        <v>-0.8216883543999999</v>
+        <v>-0.8389173172000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.511110104993979</v>
+        <v>4.976420209987958</v>
       </c>
       <c r="T100">
-        <v>45.15302035411246</v>
+        <v>90.30604070822493</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05399219921913898</v>
+        <v>0.05344682346945072</v>
       </c>
       <c r="W100">
-        <v>0.223068639424127</v>
+        <v>0.2231972390259035</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.35994799479426</v>
+        <v>0.3563121564630047</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2707294687355241</v>
-      </c>
-      <c r="C101">
-        <v>-6.39661555746476</v>
-      </c>
-      <c r="D101">
-        <v>1.95342444253524</v>
-      </c>
-      <c r="E101">
-        <v>8.43404</v>
-      </c>
-      <c r="F101">
-        <v>8.51004</v>
-      </c>
-      <c r="G101">
-        <v>0.16</v>
-      </c>
-      <c r="H101">
-        <v>8.52</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.974</v>
-      </c>
-      <c r="K101">
-        <v>0.259</v>
-      </c>
-      <c r="L101">
-        <v>0.715</v>
-      </c>
-      <c r="M101">
-        <v>2.006667432</v>
-      </c>
-      <c r="N101">
-        <v>-1.291667432</v>
-      </c>
-      <c r="O101">
-        <v>-0.1937501148</v>
-      </c>
-      <c r="P101">
-        <v>-1.0979173172</v>
-      </c>
-      <c r="Q101">
-        <v>-0.8389173172000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.976420209987958</v>
-      </c>
-      <c r="T101">
-        <v>90.30604070822493</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05344682346945072</v>
-      </c>
-      <c r="W101">
-        <v>0.2231972390259035</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3563121564630047</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
